--- a/output/version3/test/20-10/MARL/IL/RL-RL with pt (+comm+it)/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-10/MARL/IL/RL-RL with pt (+comm+it)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1023</v>
+        <v>842</v>
       </c>
       <c r="C2" t="n">
-        <v>729</v>
+        <v>864</v>
       </c>
       <c r="D2" t="n">
-        <v>881</v>
+        <v>942</v>
       </c>
       <c r="E2" t="n">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="F2" t="n">
-        <v>891</v>
+        <v>937</v>
       </c>
       <c r="G2" t="n">
-        <v>833</v>
+        <v>921</v>
       </c>
       <c r="H2" t="n">
-        <v>958</v>
+        <v>789</v>
       </c>
       <c r="I2" t="n">
-        <v>966</v>
+        <v>773</v>
       </c>
       <c r="J2" t="n">
-        <v>875</v>
+        <v>924</v>
       </c>
       <c r="K2" t="n">
-        <v>898</v>
+        <v>831</v>
       </c>
       <c r="L2" t="n">
-        <v>886.5</v>
+        <v>861.5</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>803</v>
+        <v>854</v>
       </c>
       <c r="C3" t="n">
-        <v>939</v>
+        <v>910</v>
       </c>
       <c r="D3" t="n">
-        <v>929</v>
+        <v>851</v>
       </c>
       <c r="E3" t="n">
-        <v>972</v>
+        <v>823</v>
       </c>
       <c r="F3" t="n">
-        <v>937</v>
+        <v>815</v>
       </c>
       <c r="G3" t="n">
-        <v>840</v>
+        <v>1118</v>
       </c>
       <c r="H3" t="n">
-        <v>965</v>
+        <v>899</v>
       </c>
       <c r="I3" t="n">
-        <v>883</v>
+        <v>852</v>
       </c>
       <c r="J3" t="n">
-        <v>865</v>
+        <v>806</v>
       </c>
       <c r="K3" t="n">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="L3" t="n">
-        <v>902.6</v>
+        <v>882.7</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>905</v>
+        <v>728</v>
       </c>
       <c r="C4" t="n">
         <v>865</v>
       </c>
       <c r="D4" t="n">
-        <v>841</v>
+        <v>863</v>
       </c>
       <c r="E4" t="n">
-        <v>844</v>
+        <v>799</v>
       </c>
       <c r="F4" t="n">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="G4" t="n">
-        <v>938</v>
+        <v>1016</v>
       </c>
       <c r="H4" t="n">
-        <v>871</v>
+        <v>956</v>
       </c>
       <c r="I4" t="n">
-        <v>735</v>
+        <v>1063</v>
       </c>
       <c r="J4" t="n">
-        <v>873</v>
+        <v>853</v>
       </c>
       <c r="K4" t="n">
-        <v>811</v>
+        <v>865</v>
       </c>
       <c r="L4" t="n">
-        <v>852</v>
+        <v>883</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>767</v>
+        <v>826</v>
       </c>
       <c r="C5" t="n">
-        <v>785</v>
+        <v>765</v>
       </c>
       <c r="D5" t="n">
-        <v>868</v>
+        <v>843</v>
       </c>
       <c r="E5" t="n">
-        <v>829</v>
+        <v>745</v>
       </c>
       <c r="F5" t="n">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G5" t="n">
-        <v>786</v>
+        <v>879</v>
       </c>
       <c r="H5" t="n">
-        <v>912</v>
+        <v>789</v>
       </c>
       <c r="I5" t="n">
-        <v>887</v>
+        <v>907</v>
       </c>
       <c r="J5" t="n">
-        <v>887</v>
+        <v>813</v>
       </c>
       <c r="K5" t="n">
-        <v>781</v>
+        <v>832</v>
       </c>
       <c r="L5" t="n">
-        <v>825.7</v>
+        <v>819</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>863</v>
+        <v>877</v>
       </c>
       <c r="C6" t="n">
-        <v>789</v>
+        <v>855</v>
       </c>
       <c r="D6" t="n">
-        <v>852</v>
+        <v>903</v>
       </c>
       <c r="E6" t="n">
-        <v>778</v>
+        <v>887</v>
       </c>
       <c r="F6" t="n">
-        <v>889</v>
+        <v>773</v>
       </c>
       <c r="G6" t="n">
-        <v>943</v>
+        <v>1024</v>
       </c>
       <c r="H6" t="n">
-        <v>792</v>
+        <v>802</v>
       </c>
       <c r="I6" t="n">
-        <v>900</v>
+        <v>857</v>
       </c>
       <c r="J6" t="n">
-        <v>736</v>
+        <v>850</v>
       </c>
       <c r="K6" t="n">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="L6" t="n">
-        <v>830.7</v>
+        <v>859.2</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>830</v>
+        <v>956</v>
       </c>
       <c r="C7" t="n">
-        <v>836</v>
+        <v>846</v>
       </c>
       <c r="D7" t="n">
-        <v>784</v>
+        <v>897</v>
       </c>
       <c r="E7" t="n">
-        <v>862</v>
+        <v>803</v>
       </c>
       <c r="F7" t="n">
-        <v>882</v>
+        <v>842</v>
       </c>
       <c r="G7" t="n">
-        <v>871</v>
+        <v>986</v>
       </c>
       <c r="H7" t="n">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="I7" t="n">
-        <v>861</v>
+        <v>729</v>
       </c>
       <c r="J7" t="n">
-        <v>827</v>
+        <v>758</v>
       </c>
       <c r="K7" t="n">
-        <v>915</v>
+        <v>928</v>
       </c>
       <c r="L7" t="n">
-        <v>851.5</v>
+        <v>858.8</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>973</v>
+        <v>883</v>
       </c>
       <c r="C8" t="n">
-        <v>895</v>
+        <v>1049</v>
       </c>
       <c r="D8" t="n">
-        <v>907</v>
+        <v>946</v>
       </c>
       <c r="E8" t="n">
-        <v>763</v>
+        <v>952</v>
       </c>
       <c r="F8" t="n">
-        <v>853</v>
+        <v>814</v>
       </c>
       <c r="G8" t="n">
-        <v>835</v>
+        <v>874</v>
       </c>
       <c r="H8" t="n">
-        <v>883</v>
+        <v>776</v>
       </c>
       <c r="I8" t="n">
-        <v>831</v>
+        <v>861</v>
       </c>
       <c r="J8" t="n">
-        <v>878</v>
+        <v>989</v>
       </c>
       <c r="K8" t="n">
-        <v>952</v>
+        <v>759</v>
       </c>
       <c r="L8" t="n">
-        <v>877</v>
+        <v>890.3</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>812</v>
+        <v>900</v>
       </c>
       <c r="C9" t="n">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="D9" t="n">
-        <v>839</v>
+        <v>942</v>
       </c>
       <c r="E9" t="n">
-        <v>894</v>
+        <v>938</v>
       </c>
       <c r="F9" t="n">
-        <v>799</v>
+        <v>841</v>
       </c>
       <c r="G9" t="n">
-        <v>825</v>
+        <v>849</v>
       </c>
       <c r="H9" t="n">
-        <v>749</v>
+        <v>904</v>
       </c>
       <c r="I9" t="n">
-        <v>873</v>
+        <v>859</v>
       </c>
       <c r="J9" t="n">
-        <v>971</v>
+        <v>835</v>
       </c>
       <c r="K9" t="n">
-        <v>871</v>
+        <v>893</v>
       </c>
       <c r="L9" t="n">
-        <v>851.9</v>
+        <v>885.2</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>719</v>
+        <v>751</v>
       </c>
       <c r="C10" t="n">
-        <v>739</v>
+        <v>808</v>
       </c>
       <c r="D10" t="n">
-        <v>727</v>
+        <v>694</v>
       </c>
       <c r="E10" t="n">
-        <v>792</v>
+        <v>864</v>
       </c>
       <c r="F10" t="n">
-        <v>774</v>
+        <v>712</v>
       </c>
       <c r="G10" t="n">
-        <v>722</v>
+        <v>747</v>
       </c>
       <c r="H10" t="n">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="I10" t="n">
-        <v>791</v>
+        <v>754</v>
       </c>
       <c r="J10" t="n">
-        <v>773</v>
+        <v>830</v>
       </c>
       <c r="K10" t="n">
-        <v>751</v>
+        <v>884</v>
       </c>
       <c r="L10" t="n">
-        <v>756.4</v>
+        <v>782.6</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="C11" t="n">
-        <v>765</v>
+        <v>894</v>
       </c>
       <c r="D11" t="n">
+        <v>899</v>
+      </c>
+      <c r="E11" t="n">
         <v>762</v>
       </c>
-      <c r="E11" t="n">
-        <v>742</v>
-      </c>
       <c r="F11" t="n">
-        <v>791</v>
+        <v>844</v>
       </c>
       <c r="G11" t="n">
-        <v>751</v>
+        <v>830</v>
       </c>
       <c r="H11" t="n">
-        <v>791</v>
+        <v>754</v>
       </c>
       <c r="I11" t="n">
-        <v>856</v>
+        <v>817</v>
       </c>
       <c r="J11" t="n">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="K11" t="n">
-        <v>707</v>
+        <v>834</v>
       </c>
       <c r="L11" t="n">
-        <v>771.7</v>
+        <v>819.7</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="C12" t="n">
-        <v>908</v>
+        <v>809</v>
       </c>
       <c r="D12" t="n">
-        <v>757</v>
+        <v>881</v>
       </c>
       <c r="E12" t="n">
-        <v>923</v>
+        <v>779</v>
       </c>
       <c r="F12" t="n">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="G12" t="n">
-        <v>786</v>
+        <v>900</v>
       </c>
       <c r="H12" t="n">
-        <v>879</v>
+        <v>796</v>
       </c>
       <c r="I12" t="n">
-        <v>872</v>
+        <v>798</v>
       </c>
       <c r="J12" t="n">
-        <v>844</v>
+        <v>886</v>
       </c>
       <c r="K12" t="n">
-        <v>801</v>
+        <v>850</v>
       </c>
       <c r="L12" t="n">
-        <v>839.1</v>
+        <v>831.6</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>774</v>
+        <v>849</v>
       </c>
       <c r="C13" t="n">
-        <v>784</v>
+        <v>819</v>
       </c>
       <c r="D13" t="n">
-        <v>752</v>
+        <v>685</v>
       </c>
       <c r="E13" t="n">
-        <v>780</v>
+        <v>875</v>
       </c>
       <c r="F13" t="n">
-        <v>969</v>
+        <v>903</v>
       </c>
       <c r="G13" t="n">
-        <v>865</v>
+        <v>850</v>
       </c>
       <c r="H13" t="n">
-        <v>787</v>
+        <v>810</v>
       </c>
       <c r="I13" t="n">
-        <v>804</v>
+        <v>883</v>
       </c>
       <c r="J13" t="n">
-        <v>892</v>
+        <v>838</v>
       </c>
       <c r="K13" t="n">
-        <v>787</v>
+        <v>902</v>
       </c>
       <c r="L13" t="n">
-        <v>819.4</v>
+        <v>841.4</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>806</v>
+        <v>780</v>
       </c>
       <c r="C14" t="n">
-        <v>839</v>
+        <v>953</v>
       </c>
       <c r="D14" t="n">
-        <v>766</v>
+        <v>932</v>
       </c>
       <c r="E14" t="n">
-        <v>921</v>
+        <v>901</v>
       </c>
       <c r="F14" t="n">
-        <v>926</v>
+        <v>1008</v>
       </c>
       <c r="G14" t="n">
-        <v>852</v>
+        <v>898</v>
       </c>
       <c r="H14" t="n">
-        <v>917</v>
+        <v>1044</v>
       </c>
       <c r="I14" t="n">
-        <v>849</v>
+        <v>784</v>
       </c>
       <c r="J14" t="n">
-        <v>867</v>
+        <v>884</v>
       </c>
       <c r="K14" t="n">
-        <v>829</v>
+        <v>853</v>
       </c>
       <c r="L14" t="n">
-        <v>857.2</v>
+        <v>903.7</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="C15" t="n">
-        <v>921</v>
+        <v>948</v>
       </c>
       <c r="D15" t="n">
-        <v>888</v>
+        <v>947</v>
       </c>
       <c r="E15" t="n">
-        <v>850</v>
+        <v>861</v>
       </c>
       <c r="F15" t="n">
-        <v>824</v>
+        <v>813</v>
       </c>
       <c r="G15" t="n">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="H15" t="n">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="I15" t="n">
-        <v>835</v>
+        <v>849</v>
       </c>
       <c r="J15" t="n">
-        <v>907</v>
+        <v>868</v>
       </c>
       <c r="K15" t="n">
-        <v>876</v>
+        <v>803</v>
       </c>
       <c r="L15" t="n">
-        <v>871.6</v>
+        <v>872</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>798</v>
+        <v>958</v>
       </c>
       <c r="C16" t="n">
-        <v>855</v>
+        <v>799</v>
       </c>
       <c r="D16" t="n">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="E16" t="n">
-        <v>882</v>
+        <v>859</v>
       </c>
       <c r="F16" t="n">
-        <v>903</v>
+        <v>923</v>
       </c>
       <c r="G16" t="n">
-        <v>878</v>
+        <v>899</v>
       </c>
       <c r="H16" t="n">
-        <v>858</v>
+        <v>924</v>
       </c>
       <c r="I16" t="n">
-        <v>739</v>
+        <v>884</v>
       </c>
       <c r="J16" t="n">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="K16" t="n">
-        <v>905</v>
+        <v>952</v>
       </c>
       <c r="L16" t="n">
-        <v>859</v>
+        <v>896.5</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="C17" t="n">
-        <v>760</v>
+        <v>775</v>
       </c>
       <c r="D17" t="n">
-        <v>775</v>
+        <v>735</v>
       </c>
       <c r="E17" t="n">
-        <v>774</v>
+        <v>818</v>
       </c>
       <c r="F17" t="n">
-        <v>680</v>
+        <v>766</v>
       </c>
       <c r="G17" t="n">
-        <v>816</v>
+        <v>767</v>
       </c>
       <c r="H17" t="n">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="I17" t="n">
-        <v>730</v>
+        <v>804</v>
       </c>
       <c r="J17" t="n">
-        <v>742</v>
+        <v>794</v>
       </c>
       <c r="K17" t="n">
-        <v>682</v>
+        <v>711</v>
       </c>
       <c r="L17" t="n">
-        <v>757.1</v>
+        <v>778.5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>925</v>
+        <v>949</v>
       </c>
       <c r="C18" t="n">
-        <v>1004</v>
+        <v>932</v>
       </c>
       <c r="D18" t="n">
-        <v>847</v>
+        <v>904</v>
       </c>
       <c r="E18" t="n">
-        <v>882</v>
+        <v>922</v>
       </c>
       <c r="F18" t="n">
-        <v>846</v>
+        <v>874</v>
       </c>
       <c r="G18" t="n">
-        <v>1015</v>
+        <v>999</v>
       </c>
       <c r="H18" t="n">
-        <v>805</v>
+        <v>884</v>
       </c>
       <c r="I18" t="n">
-        <v>905</v>
+        <v>994</v>
       </c>
       <c r="J18" t="n">
-        <v>1098</v>
+        <v>1067</v>
       </c>
       <c r="K18" t="n">
-        <v>1022</v>
+        <v>906</v>
       </c>
       <c r="L18" t="n">
-        <v>934.9</v>
+        <v>943.1</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C19" t="n">
-        <v>758</v>
+        <v>822</v>
       </c>
       <c r="D19" t="n">
-        <v>739</v>
+        <v>800</v>
       </c>
       <c r="E19" t="n">
-        <v>705</v>
+        <v>682</v>
       </c>
       <c r="F19" t="n">
-        <v>811</v>
+        <v>777</v>
       </c>
       <c r="G19" t="n">
-        <v>744</v>
+        <v>760</v>
       </c>
       <c r="H19" t="n">
-        <v>843</v>
+        <v>721</v>
       </c>
       <c r="I19" t="n">
-        <v>721</v>
+        <v>738</v>
       </c>
       <c r="J19" t="n">
-        <v>734</v>
+        <v>756</v>
       </c>
       <c r="K19" t="n">
-        <v>818</v>
+        <v>752</v>
       </c>
       <c r="L19" t="n">
-        <v>757.1</v>
+        <v>750</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>728</v>
+        <v>760</v>
       </c>
       <c r="C20" t="n">
-        <v>741</v>
+        <v>709</v>
       </c>
       <c r="D20" t="n">
-        <v>769</v>
+        <v>711</v>
       </c>
       <c r="E20" t="n">
-        <v>879</v>
+        <v>756</v>
       </c>
       <c r="F20" t="n">
-        <v>737</v>
+        <v>778</v>
       </c>
       <c r="G20" t="n">
-        <v>718</v>
+        <v>819</v>
       </c>
       <c r="H20" t="n">
-        <v>750</v>
+        <v>829</v>
       </c>
       <c r="I20" t="n">
-        <v>763</v>
+        <v>798</v>
       </c>
       <c r="J20" t="n">
-        <v>808</v>
+        <v>822</v>
       </c>
       <c r="K20" t="n">
-        <v>824</v>
+        <v>672</v>
       </c>
       <c r="L20" t="n">
-        <v>771.7</v>
+        <v>765.4</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>861</v>
+        <v>949</v>
       </c>
       <c r="C21" t="n">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="D21" t="n">
-        <v>721</v>
+        <v>942</v>
       </c>
       <c r="E21" t="n">
-        <v>834</v>
+        <v>936</v>
       </c>
       <c r="F21" t="n">
-        <v>868</v>
+        <v>917</v>
       </c>
       <c r="G21" t="n">
-        <v>789</v>
+        <v>931</v>
       </c>
       <c r="H21" t="n">
-        <v>881</v>
+        <v>912</v>
       </c>
       <c r="I21" t="n">
-        <v>814</v>
+        <v>897</v>
       </c>
       <c r="J21" t="n">
-        <v>871</v>
+        <v>909</v>
       </c>
       <c r="K21" t="n">
-        <v>813</v>
+        <v>993</v>
       </c>
       <c r="L21" t="n">
-        <v>832</v>
+        <v>926.2</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>873</v>
+        <v>862</v>
       </c>
       <c r="C22" t="n">
-        <v>832</v>
+        <v>846</v>
       </c>
       <c r="D22" t="n">
-        <v>817</v>
+        <v>763</v>
       </c>
       <c r="E22" t="n">
-        <v>901</v>
+        <v>831</v>
       </c>
       <c r="F22" t="n">
-        <v>793</v>
+        <v>816</v>
       </c>
       <c r="G22" t="n">
-        <v>876</v>
+        <v>900</v>
       </c>
       <c r="H22" t="n">
-        <v>906</v>
+        <v>791</v>
       </c>
       <c r="I22" t="n">
-        <v>784</v>
+        <v>829</v>
       </c>
       <c r="J22" t="n">
-        <v>882</v>
+        <v>921</v>
       </c>
       <c r="K22" t="n">
-        <v>871</v>
+        <v>900</v>
       </c>
       <c r="L22" t="n">
-        <v>853.5</v>
+        <v>845.9</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>990</v>
+        <v>879</v>
       </c>
       <c r="C23" t="n">
-        <v>948</v>
+        <v>926</v>
       </c>
       <c r="D23" t="n">
-        <v>822</v>
+        <v>914</v>
       </c>
       <c r="E23" t="n">
-        <v>890</v>
+        <v>843</v>
       </c>
       <c r="F23" t="n">
-        <v>977</v>
+        <v>1035</v>
       </c>
       <c r="G23" t="n">
-        <v>947</v>
+        <v>856</v>
       </c>
       <c r="H23" t="n">
-        <v>966</v>
+        <v>856</v>
       </c>
       <c r="I23" t="n">
-        <v>862</v>
+        <v>836</v>
       </c>
       <c r="J23" t="n">
-        <v>837</v>
+        <v>853</v>
       </c>
       <c r="K23" t="n">
-        <v>987</v>
+        <v>905</v>
       </c>
       <c r="L23" t="n">
-        <v>922.6</v>
+        <v>890.3</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>761</v>
+        <v>872</v>
       </c>
       <c r="C24" t="n">
-        <v>812</v>
+        <v>727</v>
       </c>
       <c r="D24" t="n">
-        <v>716</v>
+        <v>879</v>
       </c>
       <c r="E24" t="n">
-        <v>749</v>
+        <v>787</v>
       </c>
       <c r="F24" t="n">
-        <v>801</v>
+        <v>764</v>
       </c>
       <c r="G24" t="n">
+        <v>965</v>
+      </c>
+      <c r="H24" t="n">
+        <v>758</v>
+      </c>
+      <c r="I24" t="n">
+        <v>832</v>
+      </c>
+      <c r="J24" t="n">
         <v>744</v>
       </c>
-      <c r="H24" t="n">
-        <v>708</v>
-      </c>
-      <c r="I24" t="n">
-        <v>769</v>
-      </c>
-      <c r="J24" t="n">
-        <v>734</v>
-      </c>
       <c r="K24" t="n">
-        <v>819</v>
+        <v>760</v>
       </c>
       <c r="L24" t="n">
-        <v>761.3</v>
+        <v>808.8</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>862</v>
+        <v>732</v>
       </c>
       <c r="C25" t="n">
-        <v>807</v>
+        <v>830</v>
       </c>
       <c r="D25" t="n">
-        <v>935</v>
+        <v>913</v>
       </c>
       <c r="E25" t="n">
-        <v>887</v>
+        <v>925</v>
       </c>
       <c r="F25" t="n">
-        <v>921</v>
+        <v>954</v>
       </c>
       <c r="G25" t="n">
-        <v>810</v>
+        <v>854</v>
       </c>
       <c r="H25" t="n">
-        <v>843</v>
+        <v>893</v>
       </c>
       <c r="I25" t="n">
-        <v>900</v>
+        <v>879</v>
       </c>
       <c r="J25" t="n">
-        <v>939</v>
+        <v>894</v>
       </c>
       <c r="K25" t="n">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="L25" t="n">
-        <v>876.6</v>
+        <v>873.2</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1000</v>
+        <v>955</v>
       </c>
       <c r="C26" t="n">
-        <v>932</v>
+        <v>856</v>
       </c>
       <c r="D26" t="n">
-        <v>906</v>
+        <v>1040</v>
       </c>
       <c r="E26" t="n">
-        <v>1020</v>
+        <v>778</v>
       </c>
       <c r="F26" t="n">
-        <v>795</v>
+        <v>993</v>
       </c>
       <c r="G26" t="n">
-        <v>935</v>
+        <v>904</v>
       </c>
       <c r="H26" t="n">
-        <v>855</v>
+        <v>1083</v>
       </c>
       <c r="I26" t="n">
-        <v>885</v>
+        <v>870</v>
       </c>
       <c r="J26" t="n">
-        <v>942</v>
+        <v>965</v>
       </c>
       <c r="K26" t="n">
-        <v>902</v>
+        <v>883</v>
       </c>
       <c r="L26" t="n">
-        <v>917.2</v>
+        <v>932.7</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>974</v>
+        <v>988</v>
       </c>
       <c r="C27" t="n">
-        <v>865</v>
+        <v>842</v>
       </c>
       <c r="D27" t="n">
-        <v>848</v>
+        <v>886</v>
       </c>
       <c r="E27" t="n">
-        <v>861</v>
+        <v>920</v>
       </c>
       <c r="F27" t="n">
-        <v>884</v>
+        <v>1078</v>
       </c>
       <c r="G27" t="n">
-        <v>883</v>
+        <v>864</v>
       </c>
       <c r="H27" t="n">
-        <v>828</v>
+        <v>903</v>
       </c>
       <c r="I27" t="n">
-        <v>880</v>
+        <v>860</v>
       </c>
       <c r="J27" t="n">
-        <v>913</v>
+        <v>786</v>
       </c>
       <c r="K27" t="n">
-        <v>919</v>
+        <v>802</v>
       </c>
       <c r="L27" t="n">
-        <v>885.5</v>
+        <v>892.9</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C28" t="n">
-        <v>694</v>
+        <v>869</v>
       </c>
       <c r="D28" t="n">
-        <v>817</v>
+        <v>750</v>
       </c>
       <c r="E28" t="n">
-        <v>819</v>
+        <v>787</v>
       </c>
       <c r="F28" t="n">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="G28" t="n">
-        <v>707</v>
+        <v>667</v>
       </c>
       <c r="H28" t="n">
-        <v>726</v>
+        <v>754</v>
       </c>
       <c r="I28" t="n">
-        <v>744</v>
+        <v>767</v>
       </c>
       <c r="J28" t="n">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K28" t="n">
-        <v>949</v>
+        <v>821</v>
       </c>
       <c r="L28" t="n">
-        <v>790.9</v>
+        <v>787.9</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>811</v>
+        <v>838</v>
       </c>
       <c r="C29" t="n">
-        <v>840</v>
+        <v>883</v>
       </c>
       <c r="D29" t="n">
-        <v>858</v>
+        <v>735</v>
       </c>
       <c r="E29" t="n">
-        <v>842</v>
+        <v>888</v>
       </c>
       <c r="F29" t="n">
-        <v>770</v>
+        <v>833</v>
       </c>
       <c r="G29" t="n">
-        <v>882</v>
+        <v>822</v>
       </c>
       <c r="H29" t="n">
-        <v>813</v>
+        <v>845</v>
       </c>
       <c r="I29" t="n">
-        <v>748</v>
+        <v>722</v>
       </c>
       <c r="J29" t="n">
-        <v>806</v>
+        <v>924</v>
       </c>
       <c r="K29" t="n">
-        <v>907</v>
+        <v>821</v>
       </c>
       <c r="L29" t="n">
-        <v>827.7</v>
+        <v>831.1</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>811</v>
+        <v>756</v>
       </c>
       <c r="C30" t="n">
+        <v>740</v>
+      </c>
+      <c r="D30" t="n">
         <v>830</v>
       </c>
-      <c r="D30" t="n">
-        <v>792</v>
-      </c>
       <c r="E30" t="n">
-        <v>824</v>
+        <v>724</v>
       </c>
       <c r="F30" t="n">
-        <v>829</v>
+        <v>877</v>
       </c>
       <c r="G30" t="n">
-        <v>843</v>
+        <v>918</v>
       </c>
       <c r="H30" t="n">
-        <v>820</v>
+        <v>880</v>
       </c>
       <c r="I30" t="n">
-        <v>778</v>
+        <v>822</v>
       </c>
       <c r="J30" t="n">
-        <v>779</v>
+        <v>878</v>
       </c>
       <c r="K30" t="n">
-        <v>864</v>
+        <v>686</v>
       </c>
       <c r="L30" t="n">
-        <v>817</v>
+        <v>811.1</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>842</v>
+        <v>939</v>
       </c>
       <c r="C31" t="n">
-        <v>896</v>
+        <v>825</v>
       </c>
       <c r="D31" t="n">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="E31" t="n">
-        <v>820</v>
+        <v>931</v>
       </c>
       <c r="F31" t="n">
-        <v>816</v>
+        <v>902</v>
       </c>
       <c r="G31" t="n">
-        <v>872</v>
+        <v>780</v>
       </c>
       <c r="H31" t="n">
-        <v>896</v>
+        <v>818</v>
       </c>
       <c r="I31" t="n">
-        <v>799</v>
+        <v>1025</v>
       </c>
       <c r="J31" t="n">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="K31" t="n">
-        <v>873</v>
+        <v>886</v>
       </c>
       <c r="L31" t="n">
-        <v>852.3</v>
+        <v>882.2</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>966</v>
+        <v>925</v>
       </c>
       <c r="C32" t="n">
-        <v>931</v>
+        <v>969</v>
       </c>
       <c r="D32" t="n">
-        <v>921</v>
+        <v>911</v>
       </c>
       <c r="E32" t="n">
-        <v>847</v>
+        <v>894</v>
       </c>
       <c r="F32" t="n">
-        <v>956</v>
+        <v>940</v>
       </c>
       <c r="G32" t="n">
-        <v>871</v>
+        <v>1049</v>
       </c>
       <c r="H32" t="n">
-        <v>1013</v>
+        <v>1088</v>
       </c>
       <c r="I32" t="n">
-        <v>936</v>
+        <v>971</v>
       </c>
       <c r="J32" t="n">
-        <v>868</v>
+        <v>928</v>
       </c>
       <c r="K32" t="n">
-        <v>954</v>
+        <v>896</v>
       </c>
       <c r="L32" t="n">
-        <v>926.3</v>
+        <v>957.1</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>936</v>
+        <v>858</v>
       </c>
       <c r="C33" t="n">
-        <v>944</v>
+        <v>875</v>
       </c>
       <c r="D33" t="n">
-        <v>800</v>
+        <v>851</v>
       </c>
       <c r="E33" t="n">
-        <v>1018</v>
+        <v>914</v>
       </c>
       <c r="F33" t="n">
-        <v>985</v>
+        <v>929</v>
       </c>
       <c r="G33" t="n">
-        <v>935</v>
+        <v>801</v>
       </c>
       <c r="H33" t="n">
-        <v>879</v>
+        <v>963</v>
       </c>
       <c r="I33" t="n">
-        <v>772</v>
+        <v>786</v>
       </c>
       <c r="J33" t="n">
-        <v>918</v>
+        <v>852</v>
       </c>
       <c r="K33" t="n">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L33" t="n">
-        <v>896.3</v>
+        <v>860.6</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1007</v>
+        <v>876</v>
       </c>
       <c r="C34" t="n">
-        <v>780</v>
+        <v>910</v>
       </c>
       <c r="D34" t="n">
-        <v>1067</v>
+        <v>934</v>
       </c>
       <c r="E34" t="n">
-        <v>888</v>
+        <v>873</v>
       </c>
       <c r="F34" t="n">
-        <v>934</v>
+        <v>829</v>
       </c>
       <c r="G34" t="n">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="H34" t="n">
-        <v>866</v>
+        <v>829</v>
       </c>
       <c r="I34" t="n">
-        <v>867</v>
+        <v>812</v>
       </c>
       <c r="J34" t="n">
-        <v>977</v>
+        <v>1026</v>
       </c>
       <c r="K34" t="n">
-        <v>959</v>
+        <v>810</v>
       </c>
       <c r="L34" t="n">
-        <v>926</v>
+        <v>880.9</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="C35" t="n">
-        <v>920</v>
+        <v>863</v>
       </c>
       <c r="D35" t="n">
-        <v>891</v>
+        <v>988</v>
       </c>
       <c r="E35" t="n">
-        <v>850</v>
+        <v>807</v>
       </c>
       <c r="F35" t="n">
-        <v>917</v>
+        <v>929</v>
       </c>
       <c r="G35" t="n">
-        <v>949</v>
+        <v>926</v>
       </c>
       <c r="H35" t="n">
-        <v>829</v>
+        <v>933</v>
       </c>
       <c r="I35" t="n">
-        <v>962</v>
+        <v>1001</v>
       </c>
       <c r="J35" t="n">
-        <v>943</v>
+        <v>926</v>
       </c>
       <c r="K35" t="n">
-        <v>893</v>
+        <v>879</v>
       </c>
       <c r="L35" t="n">
-        <v>899.2</v>
+        <v>909.8</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C36" t="n">
-        <v>885</v>
+        <v>851</v>
       </c>
       <c r="D36" t="n">
-        <v>816</v>
+        <v>876</v>
       </c>
       <c r="E36" t="n">
-        <v>862</v>
+        <v>946</v>
       </c>
       <c r="F36" t="n">
-        <v>816</v>
+        <v>876</v>
       </c>
       <c r="G36" t="n">
-        <v>805</v>
+        <v>856</v>
       </c>
       <c r="H36" t="n">
-        <v>869</v>
+        <v>773</v>
       </c>
       <c r="I36" t="n">
-        <v>745</v>
+        <v>916</v>
       </c>
       <c r="J36" t="n">
-        <v>880</v>
+        <v>785</v>
       </c>
       <c r="K36" t="n">
-        <v>851</v>
+        <v>803</v>
       </c>
       <c r="L36" t="n">
-        <v>834.2</v>
+        <v>850</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>823</v>
+        <v>839</v>
       </c>
       <c r="C37" t="n">
-        <v>890</v>
+        <v>842</v>
       </c>
       <c r="D37" t="n">
-        <v>986</v>
+        <v>869</v>
       </c>
       <c r="E37" t="n">
-        <v>928</v>
+        <v>880</v>
       </c>
       <c r="F37" t="n">
-        <v>837</v>
+        <v>851</v>
       </c>
       <c r="G37" t="n">
-        <v>821</v>
+        <v>848</v>
       </c>
       <c r="H37" t="n">
-        <v>830</v>
+        <v>799</v>
       </c>
       <c r="I37" t="n">
-        <v>750</v>
+        <v>826</v>
       </c>
       <c r="J37" t="n">
-        <v>862</v>
+        <v>961</v>
       </c>
       <c r="K37" t="n">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="L37" t="n">
-        <v>859</v>
+        <v>856.2</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="C38" t="n">
-        <v>800</v>
+        <v>884</v>
       </c>
       <c r="D38" t="n">
-        <v>768</v>
+        <v>805</v>
       </c>
       <c r="E38" t="n">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="F38" t="n">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="G38" t="n">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="H38" t="n">
-        <v>812</v>
+        <v>751</v>
       </c>
       <c r="I38" t="n">
-        <v>775</v>
+        <v>856</v>
       </c>
       <c r="J38" t="n">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="K38" t="n">
-        <v>855</v>
+        <v>758</v>
       </c>
       <c r="L38" t="n">
-        <v>785.8</v>
+        <v>790.4</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>853</v>
+        <v>816</v>
       </c>
       <c r="C39" t="n">
-        <v>959</v>
+        <v>922</v>
       </c>
       <c r="D39" t="n">
-        <v>948</v>
+        <v>835</v>
       </c>
       <c r="E39" t="n">
-        <v>777</v>
+        <v>890</v>
       </c>
       <c r="F39" t="n">
-        <v>798</v>
+        <v>834</v>
       </c>
       <c r="G39" t="n">
-        <v>766</v>
+        <v>849</v>
       </c>
       <c r="H39" t="n">
-        <v>959</v>
+        <v>897</v>
       </c>
       <c r="I39" t="n">
-        <v>803</v>
+        <v>868</v>
       </c>
       <c r="J39" t="n">
-        <v>757</v>
+        <v>920</v>
       </c>
       <c r="K39" t="n">
-        <v>873</v>
+        <v>928</v>
       </c>
       <c r="L39" t="n">
-        <v>849.3</v>
+        <v>875.9</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>793</v>
+        <v>894</v>
       </c>
       <c r="C40" t="n">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="D40" t="n">
-        <v>800</v>
+        <v>821</v>
       </c>
       <c r="E40" t="n">
-        <v>725</v>
+        <v>799</v>
       </c>
       <c r="F40" t="n">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="G40" t="n">
-        <v>772</v>
+        <v>740</v>
       </c>
       <c r="H40" t="n">
-        <v>855</v>
+        <v>815</v>
       </c>
       <c r="I40" t="n">
-        <v>753</v>
+        <v>814</v>
       </c>
       <c r="J40" t="n">
-        <v>866</v>
+        <v>781</v>
       </c>
       <c r="K40" t="n">
-        <v>797</v>
+        <v>726</v>
       </c>
       <c r="L40" t="n">
-        <v>798.5</v>
+        <v>800.4</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>776</v>
+        <v>813</v>
       </c>
       <c r="C41" t="n">
-        <v>781</v>
+        <v>751</v>
       </c>
       <c r="D41" t="n">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E41" t="n">
-        <v>703</v>
+        <v>766</v>
       </c>
       <c r="F41" t="n">
-        <v>812</v>
+        <v>897</v>
       </c>
       <c r="G41" t="n">
-        <v>803</v>
+        <v>690</v>
       </c>
       <c r="H41" t="n">
-        <v>856</v>
+        <v>700</v>
       </c>
       <c r="I41" t="n">
-        <v>815</v>
+        <v>787</v>
       </c>
       <c r="J41" t="n">
-        <v>666</v>
+        <v>737</v>
       </c>
       <c r="K41" t="n">
-        <v>752</v>
+        <v>656</v>
       </c>
       <c r="L41" t="n">
-        <v>773.6</v>
+        <v>756.8</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="C42" t="n">
-        <v>888</v>
+        <v>930</v>
       </c>
       <c r="D42" t="n">
-        <v>965</v>
+        <v>680</v>
       </c>
       <c r="E42" t="n">
-        <v>828</v>
+        <v>948</v>
       </c>
       <c r="F42" t="n">
-        <v>788</v>
+        <v>820</v>
       </c>
       <c r="G42" t="n">
-        <v>942</v>
+        <v>882</v>
       </c>
       <c r="H42" t="n">
-        <v>811</v>
+        <v>682</v>
       </c>
       <c r="I42" t="n">
-        <v>763</v>
+        <v>807</v>
       </c>
       <c r="J42" t="n">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="K42" t="n">
-        <v>822</v>
+        <v>912</v>
       </c>
       <c r="L42" t="n">
-        <v>837.2</v>
+        <v>821.1</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>825</v>
+        <v>790</v>
       </c>
       <c r="C43" t="n">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="D43" t="n">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="E43" t="n">
-        <v>834</v>
+        <v>765</v>
       </c>
       <c r="F43" t="n">
-        <v>925</v>
+        <v>746</v>
       </c>
       <c r="G43" t="n">
-        <v>865</v>
+        <v>794</v>
       </c>
       <c r="H43" t="n">
-        <v>857</v>
+        <v>761</v>
       </c>
       <c r="I43" t="n">
-        <v>918</v>
+        <v>828</v>
       </c>
       <c r="J43" t="n">
-        <v>884</v>
+        <v>898</v>
       </c>
       <c r="K43" t="n">
-        <v>724</v>
+        <v>810</v>
       </c>
       <c r="L43" t="n">
-        <v>847.5</v>
+        <v>804.4</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="C44" t="n">
-        <v>702</v>
+        <v>829</v>
       </c>
       <c r="D44" t="n">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="E44" t="n">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="F44" t="n">
-        <v>795</v>
+        <v>735</v>
       </c>
       <c r="G44" t="n">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="H44" t="n">
-        <v>811</v>
+        <v>949</v>
       </c>
       <c r="I44" t="n">
-        <v>809</v>
+        <v>735</v>
       </c>
       <c r="J44" t="n">
-        <v>900</v>
+        <v>703</v>
       </c>
       <c r="K44" t="n">
-        <v>691</v>
+        <v>785</v>
       </c>
       <c r="L44" t="n">
-        <v>768</v>
+        <v>770.4</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>932</v>
+        <v>1101</v>
       </c>
       <c r="C45" t="n">
-        <v>922</v>
+        <v>985</v>
       </c>
       <c r="D45" t="n">
-        <v>941</v>
+        <v>898</v>
       </c>
       <c r="E45" t="n">
-        <v>1162</v>
+        <v>852</v>
       </c>
       <c r="F45" t="n">
-        <v>964</v>
+        <v>901</v>
       </c>
       <c r="G45" t="n">
-        <v>1018</v>
+        <v>957</v>
       </c>
       <c r="H45" t="n">
-        <v>1063</v>
+        <v>980</v>
       </c>
       <c r="I45" t="n">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="J45" t="n">
-        <v>963</v>
+        <v>997</v>
       </c>
       <c r="K45" t="n">
-        <v>978</v>
+        <v>921</v>
       </c>
       <c r="L45" t="n">
-        <v>987.7</v>
+        <v>953.8</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>884</v>
+        <v>816</v>
       </c>
       <c r="C46" t="n">
-        <v>930</v>
+        <v>888</v>
       </c>
       <c r="D46" t="n">
-        <v>873</v>
+        <v>907</v>
       </c>
       <c r="E46" t="n">
-        <v>851</v>
+        <v>762</v>
       </c>
       <c r="F46" t="n">
-        <v>758</v>
+        <v>786</v>
       </c>
       <c r="G46" t="n">
-        <v>875</v>
+        <v>912</v>
       </c>
       <c r="H46" t="n">
-        <v>816</v>
+        <v>915</v>
       </c>
       <c r="I46" t="n">
-        <v>899</v>
+        <v>858</v>
       </c>
       <c r="J46" t="n">
-        <v>763</v>
+        <v>803</v>
       </c>
       <c r="K46" t="n">
-        <v>826</v>
+        <v>918</v>
       </c>
       <c r="L46" t="n">
-        <v>847.5</v>
+        <v>856.5</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>828</v>
+        <v>877</v>
       </c>
       <c r="C47" t="n">
-        <v>924</v>
+        <v>782</v>
       </c>
       <c r="D47" t="n">
-        <v>732</v>
+        <v>882</v>
       </c>
       <c r="E47" t="n">
-        <v>820</v>
+        <v>904</v>
       </c>
       <c r="F47" t="n">
-        <v>912</v>
+        <v>871</v>
       </c>
       <c r="G47" t="n">
-        <v>815</v>
+        <v>905</v>
       </c>
       <c r="H47" t="n">
-        <v>862</v>
+        <v>981</v>
       </c>
       <c r="I47" t="n">
-        <v>888</v>
+        <v>911</v>
       </c>
       <c r="J47" t="n">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="K47" t="n">
-        <v>916</v>
+        <v>934</v>
       </c>
       <c r="L47" t="n">
-        <v>859.5</v>
+        <v>894.6</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="C48" t="n">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="D48" t="n">
-        <v>828</v>
+        <v>737</v>
       </c>
       <c r="E48" t="n">
-        <v>857</v>
+        <v>778</v>
       </c>
       <c r="F48" t="n">
-        <v>752</v>
+        <v>762</v>
       </c>
       <c r="G48" t="n">
-        <v>687</v>
+        <v>753</v>
       </c>
       <c r="H48" t="n">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="I48" t="n">
-        <v>823</v>
+        <v>832</v>
       </c>
       <c r="J48" t="n">
-        <v>751</v>
+        <v>712</v>
       </c>
       <c r="K48" t="n">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="L48" t="n">
-        <v>760.8</v>
+        <v>747.3</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C49" t="n">
-        <v>765</v>
+        <v>887</v>
       </c>
       <c r="D49" t="n">
-        <v>848</v>
+        <v>796</v>
       </c>
       <c r="E49" t="n">
-        <v>737</v>
+        <v>803</v>
       </c>
       <c r="F49" t="n">
-        <v>833</v>
+        <v>869</v>
       </c>
       <c r="G49" t="n">
-        <v>870</v>
+        <v>823</v>
       </c>
       <c r="H49" t="n">
-        <v>840</v>
+        <v>853</v>
       </c>
       <c r="I49" t="n">
-        <v>887</v>
+        <v>841</v>
       </c>
       <c r="J49" t="n">
-        <v>790</v>
+        <v>801</v>
       </c>
       <c r="K49" t="n">
-        <v>787</v>
+        <v>819</v>
       </c>
       <c r="L49" t="n">
-        <v>821.1</v>
+        <v>834.4</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>795</v>
+        <v>936</v>
       </c>
       <c r="C50" t="n">
-        <v>927</v>
+        <v>803</v>
       </c>
       <c r="D50" t="n">
-        <v>820</v>
+        <v>771</v>
       </c>
       <c r="E50" t="n">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F50" t="n">
-        <v>806</v>
+        <v>843</v>
       </c>
       <c r="G50" t="n">
-        <v>848</v>
+        <v>807</v>
       </c>
       <c r="H50" t="n">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="I50" t="n">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="J50" t="n">
-        <v>845</v>
+        <v>854</v>
       </c>
       <c r="K50" t="n">
-        <v>753</v>
+        <v>781</v>
       </c>
       <c r="L50" t="n">
-        <v>822.2</v>
+        <v>825</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>814</v>
+        <v>886</v>
       </c>
       <c r="C51" t="n">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="D51" t="n">
-        <v>821</v>
+        <v>904</v>
       </c>
       <c r="E51" t="n">
-        <v>782</v>
+        <v>743</v>
       </c>
       <c r="F51" t="n">
-        <v>837</v>
+        <v>922</v>
       </c>
       <c r="G51" t="n">
-        <v>870</v>
+        <v>827</v>
       </c>
       <c r="H51" t="n">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="I51" t="n">
-        <v>926</v>
+        <v>803</v>
       </c>
       <c r="J51" t="n">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="K51" t="n">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="L51" t="n">
-        <v>849.8</v>
+        <v>851.8</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>840.42</v>
+        <v>848.4400000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>846.62</v>
+        <v>855.26</v>
       </c>
       <c r="D52" t="n">
-        <v>836.8</v>
+        <v>851.46</v>
       </c>
       <c r="E52" t="n">
-        <v>843.4</v>
+        <v>837.4</v>
       </c>
       <c r="F52" t="n">
-        <v>844.98</v>
+        <v>856.38</v>
       </c>
       <c r="G52" t="n">
-        <v>842.1799999999999</v>
+        <v>866.14</v>
       </c>
       <c r="H52" t="n">
-        <v>849.24</v>
+        <v>849.1</v>
       </c>
       <c r="I52" t="n">
-        <v>830.4</v>
+        <v>845.98</v>
       </c>
       <c r="J52" t="n">
-        <v>851.86</v>
+        <v>855.8</v>
       </c>
       <c r="K52" t="n">
-        <v>845.9400000000001</v>
+        <v>834.8200000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>843.184</v>
+        <v>850.078</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>10.28376030921936</v>
+        <v>7.491446018218994</v>
       </c>
       <c r="C2" t="n">
-        <v>7.039682149887085</v>
+        <v>8.008646726608276</v>
       </c>
       <c r="D2" t="n">
-        <v>8.667927265167236</v>
+        <v>7.320018529891968</v>
       </c>
       <c r="E2" t="n">
-        <v>7.215204954147339</v>
+        <v>7.496458053588867</v>
       </c>
       <c r="F2" t="n">
-        <v>8.28345799446106</v>
+        <v>8.104371309280396</v>
       </c>
       <c r="G2" t="n">
-        <v>7.102992296218872</v>
+        <v>8.344771862030029</v>
       </c>
       <c r="H2" t="n">
-        <v>8.698856592178345</v>
+        <v>7.207660675048828</v>
       </c>
       <c r="I2" t="n">
-        <v>9.077364206314087</v>
+        <v>7.504949808120728</v>
       </c>
       <c r="J2" t="n">
-        <v>8.670941591262817</v>
+        <v>7.569215536117554</v>
       </c>
       <c r="K2" t="n">
-        <v>7.774763345718384</v>
+        <v>8.082950353622437</v>
       </c>
       <c r="L2" t="n">
-        <v>8.281495070457458</v>
+        <v>7.713048887252808</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>7.623137950897217</v>
+        <v>8.143818616867065</v>
       </c>
       <c r="C3" t="n">
-        <v>8.305874109268188</v>
+        <v>7.917731285095215</v>
       </c>
       <c r="D3" t="n">
-        <v>7.865003108978271</v>
+        <v>7.30951714515686</v>
       </c>
       <c r="E3" t="n">
-        <v>9.367090940475464</v>
+        <v>7.80672025680542</v>
       </c>
       <c r="F3" t="n">
-        <v>7.941351175308228</v>
+        <v>7.526961326599121</v>
       </c>
       <c r="G3" t="n">
-        <v>7.737337827682495</v>
+        <v>9.512759208679199</v>
       </c>
       <c r="H3" t="n">
-        <v>8.782660007476807</v>
+        <v>7.661095380783081</v>
       </c>
       <c r="I3" t="n">
-        <v>7.854069232940674</v>
+        <v>7.92057204246521</v>
       </c>
       <c r="J3" t="n">
-        <v>8.033089399337769</v>
+        <v>7.961344003677368</v>
       </c>
       <c r="K3" t="n">
-        <v>8.006187677383423</v>
+        <v>8.519453763961792</v>
       </c>
       <c r="L3" t="n">
-        <v>8.151580142974854</v>
+        <v>8.027997303009034</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>9.110763788223267</v>
+        <v>7.102418184280396</v>
       </c>
       <c r="C4" t="n">
-        <v>7.776785612106323</v>
+        <v>8.192162036895752</v>
       </c>
       <c r="D4" t="n">
-        <v>8.356739282608032</v>
+        <v>7.904402256011963</v>
       </c>
       <c r="E4" t="n">
-        <v>7.94779372215271</v>
+        <v>7.598672389984131</v>
       </c>
       <c r="F4" t="n">
-        <v>7.798686504364014</v>
+        <v>7.801652431488037</v>
       </c>
       <c r="G4" t="n">
-        <v>8.092426538467407</v>
+        <v>9.39509129524231</v>
       </c>
       <c r="H4" t="n">
-        <v>7.968759775161743</v>
+        <v>8.472825527191162</v>
       </c>
       <c r="I4" t="n">
-        <v>7.121953248977661</v>
+        <v>9.619507789611816</v>
       </c>
       <c r="J4" t="n">
-        <v>8.553770542144775</v>
+        <v>7.536354780197144</v>
       </c>
       <c r="K4" t="n">
-        <v>7.92689037322998</v>
+        <v>7.717856168746948</v>
       </c>
       <c r="L4" t="n">
-        <v>8.065456938743591</v>
+        <v>8.134094285964967</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>7.37830638885498</v>
+        <v>6.845572233200073</v>
       </c>
       <c r="C5" t="n">
-        <v>7.390742540359497</v>
+        <v>7.244072914123535</v>
       </c>
       <c r="D5" t="n">
-        <v>7.949830532073975</v>
+        <v>8.06547737121582</v>
       </c>
       <c r="E5" t="n">
-        <v>7.136441469192505</v>
+        <v>7.26308012008667</v>
       </c>
       <c r="F5" t="n">
-        <v>8.006186485290527</v>
+        <v>7.169280767440796</v>
       </c>
       <c r="G5" t="n">
-        <v>7.375878810882568</v>
+        <v>7.502468824386597</v>
       </c>
       <c r="H5" t="n">
-        <v>8.685359239578247</v>
+        <v>7.225104093551636</v>
       </c>
       <c r="I5" t="n">
-        <v>7.561216115951538</v>
+        <v>7.529487371444702</v>
       </c>
       <c r="J5" t="n">
-        <v>7.640514612197876</v>
+        <v>7.035095453262329</v>
       </c>
       <c r="K5" t="n">
-        <v>7.443537473678589</v>
+        <v>7.51841139793396</v>
       </c>
       <c r="L5" t="n">
-        <v>7.656801366806031</v>
+        <v>7.339805054664612</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>8.012580633163452</v>
+        <v>7.432876348495483</v>
       </c>
       <c r="C6" t="n">
-        <v>7.498388767242432</v>
+        <v>7.527948617935181</v>
       </c>
       <c r="D6" t="n">
-        <v>7.908836126327515</v>
+        <v>6.933465719223022</v>
       </c>
       <c r="E6" t="n">
-        <v>7.489392995834351</v>
+        <v>7.737398147583008</v>
       </c>
       <c r="F6" t="n">
-        <v>8.932710647583008</v>
+        <v>7.524969816207886</v>
       </c>
       <c r="G6" t="n">
-        <v>8.194116592407227</v>
+        <v>9.96508526802063</v>
       </c>
       <c r="H6" t="n">
-        <v>7.609603881835938</v>
+        <v>7.241170167922974</v>
       </c>
       <c r="I6" t="n">
-        <v>7.829031944274902</v>
+        <v>7.150891542434692</v>
       </c>
       <c r="J6" t="n">
-        <v>7.092412710189819</v>
+        <v>7.437646865844727</v>
       </c>
       <c r="K6" t="n">
-        <v>7.849021673202515</v>
+        <v>7.228712320327759</v>
       </c>
       <c r="L6" t="n">
-        <v>7.841609597206116</v>
+        <v>7.618016481399536</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>8.347736358642578</v>
+        <v>8.63457179069519</v>
       </c>
       <c r="C7" t="n">
-        <v>8.432510614395142</v>
+        <v>7.762357473373413</v>
       </c>
       <c r="D7" t="n">
-        <v>8.101851463317871</v>
+        <v>7.997711420059204</v>
       </c>
       <c r="E7" t="n">
-        <v>8.255961894989014</v>
+        <v>8.272319793701172</v>
       </c>
       <c r="F7" t="n">
-        <v>8.908803462982178</v>
+        <v>7.877955675125122</v>
       </c>
       <c r="G7" t="n">
-        <v>11.3887984752655</v>
+        <v>10.00452780723572</v>
       </c>
       <c r="H7" t="n">
-        <v>9.354230403900146</v>
+        <v>9.104337453842163</v>
       </c>
       <c r="I7" t="n">
-        <v>8.183641672134399</v>
+        <v>7.478475093841553</v>
       </c>
       <c r="J7" t="n">
-        <v>8.604102849960327</v>
+        <v>8.007659912109375</v>
       </c>
       <c r="K7" t="n">
-        <v>7.914346218109131</v>
+        <v>9.613631725311279</v>
       </c>
       <c r="L7" t="n">
-        <v>8.749198341369629</v>
+        <v>8.475354814529419</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>8.590102195739746</v>
+        <v>7.837148189544678</v>
       </c>
       <c r="C8" t="n">
-        <v>7.610623359680176</v>
+        <v>9.051981925964355</v>
       </c>
       <c r="D8" t="n">
-        <v>7.552231788635254</v>
+        <v>8.428043603897095</v>
       </c>
       <c r="E8" t="n">
-        <v>7.607649803161621</v>
+        <v>8.564704179763794</v>
       </c>
       <c r="F8" t="n">
-        <v>7.974693536758423</v>
+        <v>7.356757402420044</v>
       </c>
       <c r="G8" t="n">
-        <v>7.843995094299316</v>
+        <v>7.692008256912231</v>
       </c>
       <c r="H8" t="n">
-        <v>8.264927864074707</v>
+        <v>7.676995515823364</v>
       </c>
       <c r="I8" t="n">
-        <v>7.765203475952148</v>
+        <v>8.06147313117981</v>
       </c>
       <c r="J8" t="n">
-        <v>7.892395734786987</v>
+        <v>8.547868490219116</v>
       </c>
       <c r="K8" t="n">
-        <v>7.524328947067261</v>
+        <v>7.642038822174072</v>
       </c>
       <c r="L8" t="n">
-        <v>7.862615180015564</v>
+        <v>8.085901951789856</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>7.794147968292236</v>
+        <v>8.423571109771729</v>
       </c>
       <c r="C9" t="n">
-        <v>8.388139247894287</v>
+        <v>7.908388137817383</v>
       </c>
       <c r="D9" t="n">
-        <v>8.318314790725708</v>
+        <v>8.429573059082031</v>
       </c>
       <c r="E9" t="n">
-        <v>8.038499355316162</v>
+        <v>8.846469163894653</v>
       </c>
       <c r="F9" t="n">
-        <v>7.215590715408325</v>
+        <v>7.518380165100098</v>
       </c>
       <c r="G9" t="n">
-        <v>7.821058511734009</v>
+        <v>8.234441518783569</v>
       </c>
       <c r="H9" t="n">
-        <v>7.722800493240356</v>
+        <v>7.669238805770874</v>
       </c>
       <c r="I9" t="n">
-        <v>7.71781849861145</v>
+        <v>7.1243577003479</v>
       </c>
       <c r="J9" t="n">
-        <v>8.174159288406372</v>
+        <v>7.90637731552124</v>
       </c>
       <c r="K9" t="n">
-        <v>7.802155017852783</v>
+        <v>7.808146953582764</v>
       </c>
       <c r="L9" t="n">
-        <v>7.899268388748169</v>
+        <v>7.986894392967224</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>6.660041093826294</v>
+        <v>6.526494979858398</v>
       </c>
       <c r="C10" t="n">
-        <v>7.00214672088623</v>
+        <v>6.532885313034058</v>
       </c>
       <c r="D10" t="n">
-        <v>6.784696340560913</v>
+        <v>6.867015361785889</v>
       </c>
       <c r="E10" t="n">
-        <v>7.005164623260498</v>
+        <v>7.487924098968506</v>
       </c>
       <c r="F10" t="n">
-        <v>7.21561336517334</v>
+        <v>6.565305948257446</v>
       </c>
       <c r="G10" t="n">
-        <v>6.617120504379272</v>
+        <v>6.834638595581055</v>
       </c>
       <c r="H10" t="n">
-        <v>6.820635080337524</v>
+        <v>6.657577276229858</v>
       </c>
       <c r="I10" t="n">
-        <v>6.801712274551392</v>
+        <v>6.874521017074585</v>
       </c>
       <c r="J10" t="n">
-        <v>6.788184881210327</v>
+        <v>6.892074346542358</v>
       </c>
       <c r="K10" t="n">
-        <v>6.784709692001343</v>
+        <v>7.403763294219971</v>
       </c>
       <c r="L10" t="n">
-        <v>6.848002457618714</v>
+        <v>6.864220023155212</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>7.210641860961914</v>
+        <v>7.437658548355103</v>
       </c>
       <c r="C11" t="n">
-        <v>6.754263639450073</v>
+        <v>6.969889640808105</v>
       </c>
       <c r="D11" t="n">
-        <v>6.59916090965271</v>
+        <v>6.839233875274658</v>
       </c>
       <c r="E11" t="n">
-        <v>6.980208396911621</v>
+        <v>6.684136390686035</v>
       </c>
       <c r="F11" t="n">
-        <v>6.676457405090332</v>
+        <v>6.511568307876587</v>
       </c>
       <c r="G11" t="n">
-        <v>6.858506202697754</v>
+        <v>6.764926910400391</v>
       </c>
       <c r="H11" t="n">
-        <v>6.670993804931641</v>
+        <v>6.688170909881592</v>
       </c>
       <c r="I11" t="n">
-        <v>6.846069097518921</v>
+        <v>7.068643569946289</v>
       </c>
       <c r="J11" t="n">
-        <v>6.819589614868164</v>
+        <v>6.563953399658203</v>
       </c>
       <c r="K11" t="n">
-        <v>6.659003496170044</v>
+        <v>6.868151187896729</v>
       </c>
       <c r="L11" t="n">
-        <v>6.807489442825317</v>
+        <v>6.839633274078369</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>8.421080827713013</v>
+        <v>7.142492771148682</v>
       </c>
       <c r="C12" t="n">
-        <v>7.786754846572876</v>
+        <v>7.21226954460144</v>
       </c>
       <c r="D12" t="n">
-        <v>7.603209972381592</v>
+        <v>6.930509090423584</v>
       </c>
       <c r="E12" t="n">
-        <v>7.944801807403564</v>
+        <v>6.592943429946899</v>
       </c>
       <c r="F12" t="n">
-        <v>7.591339826583862</v>
+        <v>7.071642398834229</v>
       </c>
       <c r="G12" t="n">
-        <v>7.550862550735474</v>
+        <v>8.158821582794189</v>
       </c>
       <c r="H12" t="n">
-        <v>7.676520109176636</v>
+        <v>7.14644718170166</v>
       </c>
       <c r="I12" t="n">
-        <v>7.42071008682251</v>
+        <v>7.215675592422485</v>
       </c>
       <c r="J12" t="n">
-        <v>7.998837232589722</v>
+        <v>7.47597336769104</v>
       </c>
       <c r="K12" t="n">
-        <v>8.204129219055176</v>
+        <v>7.360793113708496</v>
       </c>
       <c r="L12" t="n">
-        <v>7.819824647903443</v>
+        <v>7.23075680732727</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>7.554845571517944</v>
+        <v>7.718877792358398</v>
       </c>
       <c r="C13" t="n">
-        <v>6.841218948364258</v>
+        <v>7.516378402709961</v>
       </c>
       <c r="D13" t="n">
-        <v>7.684482097625732</v>
+        <v>7.056081056594849</v>
       </c>
       <c r="E13" t="n">
-        <v>7.119629621505737</v>
+        <v>7.959787607192993</v>
       </c>
       <c r="F13" t="n">
-        <v>9.603063106536865</v>
+        <v>7.298941373825073</v>
       </c>
       <c r="G13" t="n">
-        <v>7.802380323410034</v>
+        <v>6.682978868484497</v>
       </c>
       <c r="H13" t="n">
-        <v>7.504853248596191</v>
+        <v>7.154804468154907</v>
       </c>
       <c r="I13" t="n">
-        <v>6.939331293106079</v>
+        <v>7.219620704650879</v>
       </c>
       <c r="J13" t="n">
-        <v>7.315860509872437</v>
+        <v>6.896942138671875</v>
       </c>
       <c r="K13" t="n">
-        <v>7.261473894119263</v>
+        <v>7.754734754562378</v>
       </c>
       <c r="L13" t="n">
-        <v>7.562713861465454</v>
+        <v>7.325914716720581</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>8.74674391746521</v>
+        <v>7.88648533821106</v>
       </c>
       <c r="C14" t="n">
-        <v>8.861418962478638</v>
+        <v>8.635027647018433</v>
       </c>
       <c r="D14" t="n">
-        <v>7.64452600479126</v>
+        <v>7.545304298400879</v>
       </c>
       <c r="E14" t="n">
-        <v>8.267447948455811</v>
+        <v>7.820080995559692</v>
       </c>
       <c r="F14" t="n">
-        <v>8.212069749832153</v>
+        <v>10.12078261375427</v>
       </c>
       <c r="G14" t="n">
-        <v>8.231002330780029</v>
+        <v>9.288861751556396</v>
       </c>
       <c r="H14" t="n">
-        <v>8.303390979766846</v>
+        <v>8.966699123382568</v>
       </c>
       <c r="I14" t="n">
-        <v>8.87736988067627</v>
+        <v>7.702913045883179</v>
       </c>
       <c r="J14" t="n">
-        <v>8.455936193466187</v>
+        <v>8.755720853805542</v>
       </c>
       <c r="K14" t="n">
-        <v>7.521314859390259</v>
+        <v>7.882946968078613</v>
       </c>
       <c r="L14" t="n">
-        <v>8.312122082710266</v>
+        <v>8.460482263565064</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>8.266932725906372</v>
+        <v>9.627639055252075</v>
       </c>
       <c r="C15" t="n">
-        <v>8.309316396713257</v>
+        <v>8.333329200744629</v>
       </c>
       <c r="D15" t="n">
-        <v>8.37765908241272</v>
+        <v>9.522275924682617</v>
       </c>
       <c r="E15" t="n">
-        <v>8.95070481300354</v>
+        <v>8.13390326499939</v>
       </c>
       <c r="F15" t="n">
-        <v>8.491891622543335</v>
+        <v>7.853598117828369</v>
       </c>
       <c r="G15" t="n">
-        <v>7.889873743057251</v>
+        <v>8.287953615188599</v>
       </c>
       <c r="H15" t="n">
-        <v>8.12180233001709</v>
+        <v>7.691527843475342</v>
       </c>
       <c r="I15" t="n">
-        <v>7.74129319190979</v>
+        <v>8.732815742492676</v>
       </c>
       <c r="J15" t="n">
-        <v>9.593074083328247</v>
+        <v>7.697545289993286</v>
       </c>
       <c r="K15" t="n">
-        <v>7.726810693740845</v>
+        <v>7.885520696640015</v>
       </c>
       <c r="L15" t="n">
-        <v>8.346935868263245</v>
+        <v>8.3766108751297</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>7.409665822982788</v>
+        <v>9.552785873413086</v>
       </c>
       <c r="C16" t="n">
-        <v>7.763225555419922</v>
+        <v>6.872137069702148</v>
       </c>
       <c r="D16" t="n">
-        <v>7.350763082504272</v>
+        <v>9.199121713638306</v>
       </c>
       <c r="E16" t="n">
-        <v>7.358245372772217</v>
+        <v>7.689527750015259</v>
       </c>
       <c r="F16" t="n">
-        <v>7.371690988540649</v>
+        <v>7.06865382194519</v>
       </c>
       <c r="G16" t="n">
-        <v>7.460507392883301</v>
+        <v>7.079125642776489</v>
       </c>
       <c r="H16" t="n">
-        <v>7.272436618804932</v>
+        <v>6.778388738632202</v>
       </c>
       <c r="I16" t="n">
-        <v>7.150286912918091</v>
+        <v>7.314460515975952</v>
       </c>
       <c r="J16" t="n">
-        <v>7.078474998474121</v>
+        <v>7.365360498428345</v>
       </c>
       <c r="K16" t="n">
-        <v>7.477468252182007</v>
+        <v>8.118390083312988</v>
       </c>
       <c r="L16" t="n">
-        <v>7.36927649974823</v>
+        <v>7.703795170783996</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>8.211082458496094</v>
+        <v>8.010253429412842</v>
       </c>
       <c r="C17" t="n">
-        <v>8.096872091293335</v>
+        <v>8.061748743057251</v>
       </c>
       <c r="D17" t="n">
-        <v>8.604078531265259</v>
+        <v>7.479567766189575</v>
       </c>
       <c r="E17" t="n">
-        <v>8.188661575317383</v>
+        <v>8.06356954574585</v>
       </c>
       <c r="F17" t="n">
-        <v>7.564744710922241</v>
+        <v>8.204965353012085</v>
       </c>
       <c r="G17" t="n">
-        <v>8.014570951461792</v>
+        <v>7.844598531723022</v>
       </c>
       <c r="H17" t="n">
-        <v>8.368171453475952</v>
+        <v>7.801817417144775</v>
       </c>
       <c r="I17" t="n">
-        <v>7.80811071395874</v>
+        <v>7.847613096237183</v>
       </c>
       <c r="J17" t="n">
-        <v>8.294366598129272</v>
+        <v>8.511365175247192</v>
       </c>
       <c r="K17" t="n">
-        <v>7.951234340667725</v>
+        <v>7.501012086868286</v>
       </c>
       <c r="L17" t="n">
-        <v>8.11018934249878</v>
+        <v>7.932651114463806</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>8.621050596237183</v>
+        <v>8.660489797592163</v>
       </c>
       <c r="C18" t="n">
-        <v>10.17753171920776</v>
+        <v>9.727291584014893</v>
       </c>
       <c r="D18" t="n">
-        <v>8.325257301330566</v>
+        <v>8.031651020050049</v>
       </c>
       <c r="E18" t="n">
-        <v>8.346706628799438</v>
+        <v>8.235581398010254</v>
       </c>
       <c r="F18" t="n">
-        <v>8.473390817642212</v>
+        <v>8.591213464736938</v>
       </c>
       <c r="G18" t="n">
-        <v>9.532223701477051</v>
+        <v>9.956867456436157</v>
       </c>
       <c r="H18" t="n">
-        <v>8.569184541702271</v>
+        <v>8.569674253463745</v>
       </c>
       <c r="I18" t="n">
-        <v>8.581605911254883</v>
+        <v>9.52922511100769</v>
       </c>
       <c r="J18" t="n">
-        <v>10.16011142730713</v>
+        <v>9.545750617980957</v>
       </c>
       <c r="K18" t="n">
-        <v>9.9192054271698</v>
+        <v>8.240160703659058</v>
       </c>
       <c r="L18" t="n">
-        <v>9.070626807212829</v>
+        <v>8.90879054069519</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>6.501938104629517</v>
+        <v>6.151853322982788</v>
       </c>
       <c r="C19" t="n">
-        <v>6.492471218109131</v>
+        <v>7.301943302154541</v>
       </c>
       <c r="D19" t="n">
-        <v>6.551305055618286</v>
+        <v>6.739415168762207</v>
       </c>
       <c r="E19" t="n">
-        <v>6.959766626358032</v>
+        <v>6.30849289894104</v>
       </c>
       <c r="F19" t="n">
-        <v>6.6705162525177</v>
+        <v>6.310457229614258</v>
       </c>
       <c r="G19" t="n">
-        <v>6.394212484359741</v>
+        <v>6.140925168991089</v>
       </c>
       <c r="H19" t="n">
-        <v>7.540800094604492</v>
+        <v>6.708482980728149</v>
       </c>
       <c r="I19" t="n">
-        <v>6.504928112030029</v>
+        <v>6.600207805633545</v>
       </c>
       <c r="J19" t="n">
-        <v>6.601673364639282</v>
+        <v>7.047072172164917</v>
       </c>
       <c r="K19" t="n">
-        <v>6.776714324951172</v>
+        <v>6.959328889846802</v>
       </c>
       <c r="L19" t="n">
-        <v>6.699432563781738</v>
+        <v>6.626817893981934</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>7.692901611328125</v>
+        <v>7.403185844421387</v>
       </c>
       <c r="C20" t="n">
-        <v>7.045023441314697</v>
+        <v>7.630580425262451</v>
       </c>
       <c r="D20" t="n">
-        <v>7.784528255462646</v>
+        <v>7.346776723861694</v>
       </c>
       <c r="E20" t="n">
-        <v>8.899843215942383</v>
+        <v>7.848180294036865</v>
       </c>
       <c r="F20" t="n">
-        <v>7.203638792037964</v>
+        <v>7.792201042175293</v>
       </c>
       <c r="G20" t="n">
-        <v>7.402126550674438</v>
+        <v>7.154802799224854</v>
       </c>
       <c r="H20" t="n">
-        <v>7.381207227706909</v>
+        <v>8.220057487487793</v>
       </c>
       <c r="I20" t="n">
-        <v>7.640529632568359</v>
+        <v>7.970212936401367</v>
       </c>
       <c r="J20" t="n">
-        <v>7.45217752456665</v>
+        <v>7.113440990447998</v>
       </c>
       <c r="K20" t="n">
-        <v>7.779761791229248</v>
+        <v>6.878639221191406</v>
       </c>
       <c r="L20" t="n">
-        <v>7.628173804283142</v>
+        <v>7.535807776451111</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>8.096455335617065</v>
+        <v>9.20445990562439</v>
       </c>
       <c r="C21" t="n">
-        <v>8.622540473937988</v>
+        <v>7.941858053207397</v>
       </c>
       <c r="D21" t="n">
-        <v>7.279040575027466</v>
+        <v>8.379221439361572</v>
       </c>
       <c r="E21" t="n">
-        <v>7.4206862449646</v>
+        <v>7.457619667053223</v>
       </c>
       <c r="F21" t="n">
-        <v>7.696463108062744</v>
+        <v>7.98425030708313</v>
       </c>
       <c r="G21" t="n">
-        <v>6.953387498855591</v>
+        <v>8.467069625854492</v>
       </c>
       <c r="H21" t="n">
-        <v>7.881978034973145</v>
+        <v>7.844611406326294</v>
       </c>
       <c r="I21" t="n">
-        <v>7.277557611465454</v>
+        <v>7.307512998580933</v>
       </c>
       <c r="J21" t="n">
-        <v>7.63211989402771</v>
+        <v>8.516656398773193</v>
       </c>
       <c r="K21" t="n">
-        <v>7.631108283996582</v>
+        <v>7.826089859008789</v>
       </c>
       <c r="L21" t="n">
-        <v>7.649133706092835</v>
+        <v>8.092934966087341</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>7.232802867889404</v>
+        <v>7.200676202774048</v>
       </c>
       <c r="C22" t="n">
-        <v>7.558311462402344</v>
+        <v>7.422114610671997</v>
       </c>
       <c r="D22" t="n">
-        <v>7.315439939498901</v>
+        <v>7.068015575408936</v>
       </c>
       <c r="E22" t="n">
-        <v>7.35735559463501</v>
+        <v>7.666072845458984</v>
       </c>
       <c r="F22" t="n">
-        <v>7.503962278366089</v>
+        <v>7.556283235549927</v>
       </c>
       <c r="G22" t="n">
-        <v>7.782732009887695</v>
+        <v>8.066506862640381</v>
       </c>
       <c r="H22" t="n">
-        <v>7.528444528579712</v>
+        <v>7.254046440124512</v>
       </c>
       <c r="I22" t="n">
-        <v>6.668632984161377</v>
+        <v>7.390193462371826</v>
       </c>
       <c r="J22" t="n">
-        <v>7.751811981201172</v>
+        <v>8.388136148452759</v>
       </c>
       <c r="K22" t="n">
-        <v>8.054035425186157</v>
+        <v>9.196689128875732</v>
       </c>
       <c r="L22" t="n">
-        <v>7.475352907180786</v>
+        <v>7.72087345123291</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>10.52708315849304</v>
+        <v>8.957677364349365</v>
       </c>
       <c r="C23" t="n">
-        <v>9.1417076587677</v>
+        <v>9.801081418991089</v>
       </c>
       <c r="D23" t="n">
-        <v>8.506329298019409</v>
+        <v>9.551728487014771</v>
       </c>
       <c r="E23" t="n">
-        <v>9.617002725601196</v>
+        <v>8.342260122299194</v>
       </c>
       <c r="F23" t="n">
-        <v>9.985982894897461</v>
+        <v>10.44742846488953</v>
       </c>
       <c r="G23" t="n">
-        <v>9.506239414215088</v>
+        <v>8.15169620513916</v>
       </c>
       <c r="H23" t="n">
-        <v>9.053907155990601</v>
+        <v>8.428490400314331</v>
       </c>
       <c r="I23" t="n">
-        <v>8.614051818847656</v>
+        <v>8.536329746246338</v>
       </c>
       <c r="J23" t="n">
-        <v>8.225020170211792</v>
+        <v>9.099838972091675</v>
       </c>
       <c r="K23" t="n">
-        <v>10.02343273162842</v>
+        <v>8.709346771240234</v>
       </c>
       <c r="L23" t="n">
-        <v>9.320075702667236</v>
+        <v>9.002587795257568</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>7.128312349319458</v>
+        <v>8.554228067398071</v>
       </c>
       <c r="C24" t="n">
-        <v>7.520334720611572</v>
+        <v>7.153273820877075</v>
       </c>
       <c r="D24" t="n">
-        <v>7.084433555603027</v>
+        <v>6.90091347694397</v>
       </c>
       <c r="E24" t="n">
-        <v>7.707884788513184</v>
+        <v>7.166300058364868</v>
       </c>
       <c r="F24" t="n">
-        <v>7.664495229721069</v>
+        <v>7.185192346572876</v>
       </c>
       <c r="G24" t="n">
-        <v>7.34928822517395</v>
+        <v>8.94678783416748</v>
       </c>
       <c r="H24" t="n">
-        <v>7.400149583816528</v>
+        <v>7.177313804626465</v>
       </c>
       <c r="I24" t="n">
-        <v>6.84855580329895</v>
+        <v>6.889967918395996</v>
       </c>
       <c r="J24" t="n">
-        <v>6.720370054244995</v>
+        <v>6.892942667007446</v>
       </c>
       <c r="K24" t="n">
-        <v>7.537283658981323</v>
+        <v>6.611699342727661</v>
       </c>
       <c r="L24" t="n">
-        <v>7.296110796928406</v>
+        <v>7.347861933708191</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>8.683434724807739</v>
+        <v>8.626938104629517</v>
       </c>
       <c r="C25" t="n">
-        <v>9.015027523040771</v>
+        <v>8.474411010742188</v>
       </c>
       <c r="D25" t="n">
-        <v>12.01737451553345</v>
+        <v>9.865415573120117</v>
       </c>
       <c r="E25" t="n">
-        <v>8.727249145507812</v>
+        <v>9.847970485687256</v>
       </c>
       <c r="F25" t="n">
-        <v>8.700295448303223</v>
+        <v>9.896331548690796</v>
       </c>
       <c r="G25" t="n">
-        <v>9.453892230987549</v>
+        <v>9.474961757659912</v>
       </c>
       <c r="H25" t="n">
-        <v>8.93248987197876</v>
+        <v>8.414596080780029</v>
       </c>
       <c r="I25" t="n">
-        <v>10.0348653793335</v>
+        <v>8.702363967895508</v>
       </c>
       <c r="J25" t="n">
-        <v>9.701241016387939</v>
+        <v>9.061841726303101</v>
       </c>
       <c r="K25" t="n">
-        <v>9.230963230133057</v>
+        <v>8.754279375076294</v>
       </c>
       <c r="L25" t="n">
-        <v>9.449683308601379</v>
+        <v>9.111910963058472</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>9.581063985824585</v>
+        <v>8.843635320663452</v>
       </c>
       <c r="C26" t="n">
-        <v>8.197581052780151</v>
+        <v>7.679946660995483</v>
       </c>
       <c r="D26" t="n">
-        <v>8.293360948562622</v>
+        <v>9.131238222122192</v>
       </c>
       <c r="E26" t="n">
-        <v>9.020997762680054</v>
+        <v>7.834032773971558</v>
       </c>
       <c r="F26" t="n">
-        <v>7.749776363372803</v>
+        <v>8.559733152389526</v>
       </c>
       <c r="G26" t="n">
-        <v>8.734770536422729</v>
+        <v>7.353307247161865</v>
       </c>
       <c r="H26" t="n">
-        <v>7.977173805236816</v>
+        <v>9.777613878250122</v>
       </c>
       <c r="I26" t="n">
-        <v>8.034544706344604</v>
+        <v>8.274433135986328</v>
       </c>
       <c r="J26" t="n">
-        <v>9.250971078872681</v>
+        <v>7.983674287796021</v>
       </c>
       <c r="K26" t="n">
-        <v>7.927269458770752</v>
+        <v>7.862993240356445</v>
       </c>
       <c r="L26" t="n">
-        <v>8.47675096988678</v>
+        <v>8.330060791969299</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>9.056904077529907</v>
+        <v>9.611597061157227</v>
       </c>
       <c r="C27" t="n">
-        <v>9.078354835510254</v>
+        <v>8.959229469299316</v>
       </c>
       <c r="D27" t="n">
-        <v>9.456884860992432</v>
+        <v>8.760968685150146</v>
       </c>
       <c r="E27" t="n">
-        <v>9.70481276512146</v>
+        <v>8.69890308380127</v>
       </c>
       <c r="F27" t="n">
-        <v>9.366459608078003</v>
+        <v>10.61338758468628</v>
       </c>
       <c r="G27" t="n">
-        <v>8.386671304702759</v>
+        <v>8.684644460678101</v>
       </c>
       <c r="H27" t="n">
-        <v>8.148740291595459</v>
+        <v>9.119744777679443</v>
       </c>
       <c r="I27" t="n">
-        <v>8.745190143585205</v>
+        <v>8.356275320053101</v>
       </c>
       <c r="J27" t="n">
-        <v>8.106046676635742</v>
+        <v>8.539346933364868</v>
       </c>
       <c r="K27" t="n">
-        <v>8.818558692932129</v>
+        <v>8.820549249649048</v>
       </c>
       <c r="L27" t="n">
-        <v>8.886862325668336</v>
+        <v>9.016464662551879</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.433525323867798</v>
+        <v>7.317957639694214</v>
       </c>
       <c r="C28" t="n">
-        <v>7.275065422058105</v>
+        <v>7.030130386352539</v>
       </c>
       <c r="D28" t="n">
-        <v>7.292520523071289</v>
+        <v>6.965299844741821</v>
       </c>
       <c r="E28" t="n">
-        <v>7.53392219543457</v>
+        <v>6.939834833145142</v>
       </c>
       <c r="F28" t="n">
-        <v>7.660043716430664</v>
+        <v>7.383681297302246</v>
       </c>
       <c r="G28" t="n">
-        <v>6.970838308334351</v>
+        <v>6.962342262268066</v>
       </c>
       <c r="H28" t="n">
-        <v>7.101022481918335</v>
+        <v>7.155322790145874</v>
       </c>
       <c r="I28" t="n">
-        <v>6.957396268844604</v>
+        <v>7.831115484237671</v>
       </c>
       <c r="J28" t="n">
-        <v>7.4127037525177</v>
+        <v>7.965782403945923</v>
       </c>
       <c r="K28" t="n">
-        <v>8.066550731658936</v>
+        <v>7.978845119476318</v>
       </c>
       <c r="L28" t="n">
-        <v>7.370358872413635</v>
+        <v>7.353031206130981</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>7.665026903152466</v>
+        <v>7.780255556106567</v>
       </c>
       <c r="C29" t="n">
-        <v>7.878020048141479</v>
+        <v>7.858011484146118</v>
       </c>
       <c r="D29" t="n">
-        <v>8.051039457321167</v>
+        <v>7.94640851020813</v>
       </c>
       <c r="E29" t="n">
-        <v>7.844799995422363</v>
+        <v>8.219233751296997</v>
       </c>
       <c r="F29" t="n">
-        <v>7.035639524459839</v>
+        <v>8.252127885818481</v>
       </c>
       <c r="G29" t="n">
-        <v>7.932286500930786</v>
+        <v>7.730036973953247</v>
       </c>
       <c r="H29" t="n">
-        <v>7.650492668151855</v>
+        <v>7.636672973632812</v>
       </c>
       <c r="I29" t="n">
-        <v>8.06295371055603</v>
+        <v>8.08594822883606</v>
       </c>
       <c r="J29" t="n">
-        <v>8.542702674865723</v>
+        <v>7.582736492156982</v>
       </c>
       <c r="K29" t="n">
-        <v>7.665440082550049</v>
+        <v>8.094910621643066</v>
       </c>
       <c r="L29" t="n">
-        <v>7.832840156555176</v>
+        <v>7.918634247779846</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>7.636536121368408</v>
+        <v>7.351815938949585</v>
       </c>
       <c r="C30" t="n">
-        <v>14.47799348831177</v>
+        <v>7.309957504272461</v>
       </c>
       <c r="D30" t="n">
-        <v>7.940282106399536</v>
+        <v>8.020629405975342</v>
       </c>
       <c r="E30" t="n">
-        <v>7.338772296905518</v>
+        <v>7.599788904190063</v>
       </c>
       <c r="F30" t="n">
-        <v>8.145241498947144</v>
+        <v>9.884398460388184</v>
       </c>
       <c r="G30" t="n">
-        <v>7.885875940322876</v>
+        <v>8.374258756637573</v>
       </c>
       <c r="H30" t="n">
-        <v>7.550764560699463</v>
+        <v>8.776781797409058</v>
       </c>
       <c r="I30" t="n">
-        <v>7.489883661270142</v>
+        <v>8.296454429626465</v>
       </c>
       <c r="J30" t="n">
-        <v>7.758847951889038</v>
+        <v>8.385247230529785</v>
       </c>
       <c r="K30" t="n">
-        <v>7.998125076293945</v>
+        <v>7.309148788452148</v>
       </c>
       <c r="L30" t="n">
-        <v>8.422232270240784</v>
+        <v>8.130848121643066</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>7.375711441040039</v>
+        <v>9.586732625961304</v>
       </c>
       <c r="C31" t="n">
-        <v>7.934264183044434</v>
+        <v>7.580719232559204</v>
       </c>
       <c r="D31" t="n">
-        <v>7.23654580116272</v>
+        <v>9.131298303604126</v>
       </c>
       <c r="E31" t="n">
-        <v>7.365190267562866</v>
+        <v>9.350797653198242</v>
       </c>
       <c r="F31" t="n">
-        <v>7.210236310958862</v>
+        <v>8.171253681182861</v>
       </c>
       <c r="G31" t="n">
-        <v>7.341401815414429</v>
+        <v>7.653570652008057</v>
       </c>
       <c r="H31" t="n">
-        <v>7.15935754776001</v>
+        <v>7.191742420196533</v>
       </c>
       <c r="I31" t="n">
-        <v>7.143921613693237</v>
+        <v>9.19621467590332</v>
       </c>
       <c r="J31" t="n">
-        <v>7.457608222961426</v>
+        <v>7.806173801422119</v>
       </c>
       <c r="K31" t="n">
-        <v>7.740358114242554</v>
+        <v>8.688478469848633</v>
       </c>
       <c r="L31" t="n">
-        <v>7.396459531784058</v>
+        <v>8.43569815158844</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>8.745787858963013</v>
+        <v>9.331274509429932</v>
       </c>
       <c r="C32" t="n">
-        <v>9.795513391494751</v>
+        <v>8.902364730834961</v>
       </c>
       <c r="D32" t="n">
-        <v>8.581184387207031</v>
+        <v>10.03251194953918</v>
       </c>
       <c r="E32" t="n">
-        <v>8.894387483596802</v>
+        <v>9.216552495956421</v>
       </c>
       <c r="F32" t="n">
-        <v>9.056421041488647</v>
+        <v>10.33530879020691</v>
       </c>
       <c r="G32" t="n">
-        <v>8.391152620315552</v>
+        <v>9.302837610244751</v>
       </c>
       <c r="H32" t="n">
-        <v>9.491814613342285</v>
+        <v>8.491904497146606</v>
       </c>
       <c r="I32" t="n">
-        <v>8.669423580169678</v>
+        <v>8.452493190765381</v>
       </c>
       <c r="J32" t="n">
-        <v>8.41411018371582</v>
+        <v>9.325805902481079</v>
       </c>
       <c r="K32" t="n">
-        <v>8.4994056224823</v>
+        <v>7.961732625961304</v>
       </c>
       <c r="L32" t="n">
-        <v>8.853920078277588</v>
+        <v>9.135278630256654</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>9.51274847984314</v>
+        <v>7.226603269577026</v>
       </c>
       <c r="C33" t="n">
-        <v>7.486489057540894</v>
+        <v>8.520861148834229</v>
       </c>
       <c r="D33" t="n">
-        <v>7.400332450866699</v>
+        <v>7.724619150161743</v>
       </c>
       <c r="E33" t="n">
-        <v>10.2587902545929</v>
+        <v>8.175233602523804</v>
       </c>
       <c r="F33" t="n">
-        <v>9.461374759674072</v>
+        <v>8.582727432250977</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01116681098938</v>
+        <v>7.479485511779785</v>
       </c>
       <c r="H33" t="n">
-        <v>7.841591358184814</v>
+        <v>7.95725417137146</v>
       </c>
       <c r="I33" t="n">
-        <v>7.139898061752319</v>
+        <v>7.310894250869751</v>
       </c>
       <c r="J33" t="n">
-        <v>8.658954620361328</v>
+        <v>7.655308485031128</v>
       </c>
       <c r="K33" t="n">
-        <v>7.2491455078125</v>
+        <v>7.713904619216919</v>
       </c>
       <c r="L33" t="n">
-        <v>8.302049136161804</v>
+        <v>7.834689164161682</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>9.768575429916382</v>
+        <v>8.33728551864624</v>
       </c>
       <c r="C34" t="n">
-        <v>7.491719961166382</v>
+        <v>8.284451484680176</v>
       </c>
       <c r="D34" t="n">
-        <v>9.457853555679321</v>
+        <v>8.190664768218994</v>
       </c>
       <c r="E34" t="n">
-        <v>9.911978721618652</v>
+        <v>7.737850666046143</v>
       </c>
       <c r="F34" t="n">
-        <v>8.490902423858643</v>
+        <v>7.767706632614136</v>
       </c>
       <c r="G34" t="n">
-        <v>8.010160684585571</v>
+        <v>7.844019651412964</v>
       </c>
       <c r="H34" t="n">
-        <v>9.154202461242676</v>
+        <v>7.883456707000732</v>
       </c>
       <c r="I34" t="n">
-        <v>8.678423404693604</v>
+        <v>7.362762928009033</v>
       </c>
       <c r="J34" t="n">
-        <v>8.221614599227905</v>
+        <v>9.45143461227417</v>
       </c>
       <c r="K34" t="n">
-        <v>8.931293725967407</v>
+        <v>7.556285619735718</v>
       </c>
       <c r="L34" t="n">
-        <v>8.811672496795655</v>
+        <v>8.04159185886383</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.87898588180542</v>
+        <v>7.692936420440674</v>
       </c>
       <c r="C35" t="n">
-        <v>8.519321918487549</v>
+        <v>7.694950342178345</v>
       </c>
       <c r="D35" t="n">
-        <v>7.909909009933472</v>
+        <v>8.446495771408081</v>
       </c>
       <c r="E35" t="n">
-        <v>8.074973344802856</v>
+        <v>7.091440439224243</v>
       </c>
       <c r="F35" t="n">
-        <v>8.076964616775513</v>
+        <v>9.202606201171875</v>
       </c>
       <c r="G35" t="n">
-        <v>8.480949878692627</v>
+        <v>7.227609634399414</v>
       </c>
       <c r="H35" t="n">
-        <v>7.474919080734253</v>
+        <v>7.65453052520752</v>
       </c>
       <c r="I35" t="n">
-        <v>9.137200832366943</v>
+        <v>8.997124671936035</v>
       </c>
       <c r="J35" t="n">
-        <v>8.384657382965088</v>
+        <v>7.594699382781982</v>
       </c>
       <c r="K35" t="n">
-        <v>7.890403270721436</v>
+        <v>7.563236951828003</v>
       </c>
       <c r="L35" t="n">
-        <v>8.182828521728515</v>
+        <v>7.916563034057617</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>8.242731094360352</v>
+        <v>7.594669818878174</v>
       </c>
       <c r="C36" t="n">
-        <v>8.125786304473877</v>
+        <v>7.844152927398682</v>
       </c>
       <c r="D36" t="n">
-        <v>7.477449893951416</v>
+        <v>7.691488027572632</v>
       </c>
       <c r="E36" t="n">
-        <v>8.011262178421021</v>
+        <v>7.774796009063721</v>
       </c>
       <c r="F36" t="n">
-        <v>7.563956499099731</v>
+        <v>7.517997741699219</v>
       </c>
       <c r="G36" t="n">
-        <v>7.790213346481323</v>
+        <v>7.853750705718994</v>
       </c>
       <c r="H36" t="n">
-        <v>7.867925643920898</v>
+        <v>7.36177659034729</v>
       </c>
       <c r="I36" t="n">
-        <v>7.559731245040894</v>
+        <v>9.128257274627686</v>
       </c>
       <c r="J36" t="n">
-        <v>8.138784885406494</v>
+        <v>7.532831430435181</v>
       </c>
       <c r="K36" t="n">
-        <v>8.947750329971313</v>
+        <v>7.827115535736084</v>
       </c>
       <c r="L36" t="n">
-        <v>7.972559142112732</v>
+        <v>7.812683606147766</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>7.167774200439453</v>
+        <v>7.741778135299683</v>
       </c>
       <c r="C37" t="n">
-        <v>7.323814630508423</v>
+        <v>7.965208530426025</v>
       </c>
       <c r="D37" t="n">
-        <v>8.443456888198853</v>
+        <v>6.906929731369019</v>
       </c>
       <c r="E37" t="n">
-        <v>7.455517053604126</v>
+        <v>7.07848596572876</v>
       </c>
       <c r="F37" t="n">
-        <v>7.511848926544189</v>
+        <v>7.303933382034302</v>
       </c>
       <c r="G37" t="n">
-        <v>7.18370246887207</v>
+        <v>7.152289867401123</v>
       </c>
       <c r="H37" t="n">
-        <v>7.895371437072754</v>
+        <v>6.941711902618408</v>
       </c>
       <c r="I37" t="n">
-        <v>7.047055721282959</v>
+        <v>7.581604957580566</v>
       </c>
       <c r="J37" t="n">
-        <v>7.116393089294434</v>
+        <v>7.995695114135742</v>
       </c>
       <c r="K37" t="n">
-        <v>7.533285856246948</v>
+        <v>8.087252616882324</v>
       </c>
       <c r="L37" t="n">
-        <v>7.467822027206421</v>
+        <v>7.475489020347595</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>7.498370170593262</v>
+        <v>6.972761631011963</v>
       </c>
       <c r="C38" t="n">
-        <v>7.226615905761719</v>
+        <v>7.822508811950684</v>
       </c>
       <c r="D38" t="n">
-        <v>7.068501234054565</v>
+        <v>6.903090715408325</v>
       </c>
       <c r="E38" t="n">
-        <v>7.066972494125366</v>
+        <v>7.263627290725708</v>
       </c>
       <c r="F38" t="n">
-        <v>7.406174659729004</v>
+        <v>7.198379993438721</v>
       </c>
       <c r="G38" t="n">
-        <v>7.077459335327148</v>
+        <v>8.033252000808716</v>
       </c>
       <c r="H38" t="n">
-        <v>7.76898193359375</v>
+        <v>7.347460269927979</v>
       </c>
       <c r="I38" t="n">
-        <v>6.885962963104248</v>
+        <v>7.944852828979492</v>
       </c>
       <c r="J38" t="n">
-        <v>7.340771198272705</v>
+        <v>7.32403039932251</v>
       </c>
       <c r="K38" t="n">
-        <v>7.256010770797729</v>
+        <v>7.494522094726562</v>
       </c>
       <c r="L38" t="n">
-        <v>7.25958206653595</v>
+        <v>7.430448603630066</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>7.804131746292114</v>
+        <v>7.816683530807495</v>
       </c>
       <c r="C39" t="n">
-        <v>8.604095220565796</v>
+        <v>8.164777755737305</v>
       </c>
       <c r="D39" t="n">
-        <v>8.924768447875977</v>
+        <v>7.908936738967896</v>
       </c>
       <c r="E39" t="n">
-        <v>7.736788511276245</v>
+        <v>8.46628737449646</v>
       </c>
       <c r="F39" t="n">
-        <v>7.770196437835693</v>
+        <v>8.01017951965332</v>
       </c>
       <c r="G39" t="n">
-        <v>8.2270188331604</v>
+        <v>7.963357210159302</v>
       </c>
       <c r="H39" t="n">
-        <v>8.705322980880737</v>
+        <v>8.524364233016968</v>
       </c>
       <c r="I39" t="n">
-        <v>7.801134347915649</v>
+        <v>8.291159152984619</v>
       </c>
       <c r="J39" t="n">
-        <v>7.407596111297607</v>
+        <v>7.701479434967041</v>
       </c>
       <c r="K39" t="n">
-        <v>8.583156824111938</v>
+        <v>7.783756256103516</v>
       </c>
       <c r="L39" t="n">
-        <v>8.156420946121216</v>
+        <v>8.063098120689393</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>7.575722694396973</v>
+        <v>9.134772062301636</v>
       </c>
       <c r="C40" t="n">
-        <v>7.822054862976074</v>
+        <v>8.052558898925781</v>
       </c>
       <c r="D40" t="n">
-        <v>7.332801580429077</v>
+        <v>7.426224946975708</v>
       </c>
       <c r="E40" t="n">
-        <v>7.36072826385498</v>
+        <v>7.92092752456665</v>
       </c>
       <c r="F40" t="n">
-        <v>7.429569005966187</v>
+        <v>7.068119764328003</v>
       </c>
       <c r="G40" t="n">
-        <v>7.326803207397461</v>
+        <v>7.139847993850708</v>
       </c>
       <c r="H40" t="n">
-        <v>8.487340927124023</v>
+        <v>7.805164098739624</v>
       </c>
       <c r="I40" t="n">
-        <v>7.64202094078064</v>
+        <v>7.401670932769775</v>
       </c>
       <c r="J40" t="n">
-        <v>8.411035299301147</v>
+        <v>7.479477643966675</v>
       </c>
       <c r="K40" t="n">
-        <v>7.823575496673584</v>
+        <v>6.923545837402344</v>
       </c>
       <c r="L40" t="n">
-        <v>7.721165227890014</v>
+        <v>7.635230970382691</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>7.375678777694702</v>
+        <v>7.290952205657959</v>
       </c>
       <c r="C41" t="n">
-        <v>7.6125807762146</v>
+        <v>7.102432727813721</v>
       </c>
       <c r="D41" t="n">
-        <v>6.727365255355835</v>
+        <v>7.336632251739502</v>
       </c>
       <c r="E41" t="n">
-        <v>7.369204044342041</v>
+        <v>6.843632221221924</v>
       </c>
       <c r="F41" t="n">
-        <v>7.747728824615479</v>
+        <v>7.538803577423096</v>
       </c>
       <c r="G41" t="n">
-        <v>7.670108556747437</v>
+        <v>7.034122228622437</v>
       </c>
       <c r="H41" t="n">
-        <v>7.540268659591675</v>
+        <v>7.140358209609985</v>
       </c>
       <c r="I41" t="n">
-        <v>8.368165016174316</v>
+        <v>7.14348578453064</v>
       </c>
       <c r="J41" t="n">
-        <v>7.380196809768677</v>
+        <v>7.100450754165649</v>
       </c>
       <c r="K41" t="n">
-        <v>7.568704128265381</v>
+        <v>6.884011268615723</v>
       </c>
       <c r="L41" t="n">
-        <v>7.536000084877014</v>
+        <v>7.141488122940063</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>7.523351907730103</v>
+        <v>7.396154880523682</v>
       </c>
       <c r="C42" t="n">
-        <v>9.401022672653198</v>
+        <v>8.403627395629883</v>
       </c>
       <c r="D42" t="n">
-        <v>9.065899133682251</v>
+        <v>6.992710590362549</v>
       </c>
       <c r="E42" t="n">
-        <v>8.616070747375488</v>
+        <v>8.672491550445557</v>
       </c>
       <c r="F42" t="n">
-        <v>7.574672222137451</v>
+        <v>7.696983814239502</v>
       </c>
       <c r="G42" t="n">
-        <v>9.062889099121094</v>
+        <v>8.278911352157593</v>
       </c>
       <c r="H42" t="n">
-        <v>8.197126626968384</v>
+        <v>7.163777589797974</v>
       </c>
       <c r="I42" t="n">
-        <v>7.825915575027466</v>
+        <v>7.57124662399292</v>
       </c>
       <c r="J42" t="n">
-        <v>7.876473188400269</v>
+        <v>7.768218994140625</v>
       </c>
       <c r="K42" t="n">
-        <v>8.021184206008911</v>
+        <v>8.928752183914185</v>
       </c>
       <c r="L42" t="n">
-        <v>8.316460537910462</v>
+        <v>7.887287497520447</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>8.15113353729248</v>
+        <v>7.129355669021606</v>
       </c>
       <c r="C43" t="n">
-        <v>7.384220361709595</v>
+        <v>7.423119068145752</v>
       </c>
       <c r="D43" t="n">
-        <v>7.988157510757446</v>
+        <v>7.482462406158447</v>
       </c>
       <c r="E43" t="n">
-        <v>8.266494274139404</v>
+        <v>7.822108268737793</v>
       </c>
       <c r="F43" t="n">
-        <v>8.220077037811279</v>
+        <v>7.625620603561401</v>
       </c>
       <c r="G43" t="n">
-        <v>8.787617921829224</v>
+        <v>8.939525604248047</v>
       </c>
       <c r="H43" t="n">
-        <v>7.499858856201172</v>
+        <v>7.804808378219604</v>
       </c>
       <c r="I43" t="n">
-        <v>9.526259899139404</v>
+        <v>8.349872589111328</v>
       </c>
       <c r="J43" t="n">
-        <v>7.898349761962891</v>
+        <v>7.859091281890869</v>
       </c>
       <c r="K43" t="n">
-        <v>7.178689241409302</v>
+        <v>7.064064979553223</v>
       </c>
       <c r="L43" t="n">
-        <v>8.090085840225219</v>
+        <v>7.750002884864807</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>6.881954669952393</v>
+        <v>6.675540924072266</v>
       </c>
       <c r="C44" t="n">
-        <v>6.847584009170532</v>
+        <v>7.245555400848389</v>
       </c>
       <c r="D44" t="n">
-        <v>6.522870779037476</v>
+        <v>6.431657075881958</v>
       </c>
       <c r="E44" t="n">
-        <v>6.384732484817505</v>
+        <v>6.461076736450195</v>
       </c>
       <c r="F44" t="n">
-        <v>7.097925901412964</v>
+        <v>6.381245374679565</v>
       </c>
       <c r="G44" t="n">
-        <v>6.643622159957886</v>
+        <v>6.887991666793823</v>
       </c>
       <c r="H44" t="n">
-        <v>7.281436920166016</v>
+        <v>7.873492002487183</v>
       </c>
       <c r="I44" t="n">
-        <v>6.620130300521851</v>
+        <v>6.665034055709839</v>
       </c>
       <c r="J44" t="n">
-        <v>7.803097486495972</v>
+        <v>6.9299156665802</v>
       </c>
       <c r="K44" t="n">
-        <v>6.277491807937622</v>
+        <v>6.372857570648193</v>
       </c>
       <c r="L44" t="n">
-        <v>6.836084651947021</v>
+        <v>6.792436647415161</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>8.757192850112915</v>
+        <v>10.11874055862427</v>
       </c>
       <c r="C45" t="n">
-        <v>9.039463996887207</v>
+        <v>8.782678604125977</v>
       </c>
       <c r="D45" t="n">
-        <v>9.208064794540405</v>
+        <v>8.152740955352783</v>
       </c>
       <c r="E45" t="n">
-        <v>9.913252830505371</v>
+        <v>8.137790441513062</v>
       </c>
       <c r="F45" t="n">
-        <v>8.508816957473755</v>
+        <v>7.989692687988281</v>
       </c>
       <c r="G45" t="n">
-        <v>9.495298147201538</v>
+        <v>8.714332103729248</v>
       </c>
       <c r="H45" t="n">
-        <v>9.207515239715576</v>
+        <v>8.940778732299805</v>
       </c>
       <c r="I45" t="n">
-        <v>9.302793264389038</v>
+        <v>8.398662328720093</v>
       </c>
       <c r="J45" t="n">
-        <v>9.50780177116394</v>
+        <v>9.521283626556396</v>
       </c>
       <c r="K45" t="n">
-        <v>8.963180303573608</v>
+        <v>8.511857986450195</v>
       </c>
       <c r="L45" t="n">
-        <v>9.190338015556335</v>
+        <v>8.726855802536011</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>9.125264644622803</v>
+        <v>7.833165168762207</v>
       </c>
       <c r="C46" t="n">
-        <v>9.082356691360474</v>
+        <v>7.614679336547852</v>
       </c>
       <c r="D46" t="n">
-        <v>7.315870523452759</v>
+        <v>8.176217079162598</v>
       </c>
       <c r="E46" t="n">
-        <v>7.394650459289551</v>
+        <v>7.224623918533325</v>
       </c>
       <c r="F46" t="n">
-        <v>7.273968696594238</v>
+        <v>7.888945579528809</v>
       </c>
       <c r="G46" t="n">
-        <v>8.138766050338745</v>
+        <v>8.585148572921753</v>
       </c>
       <c r="H46" t="n">
-        <v>7.241549015045166</v>
+        <v>8.184176683425903</v>
       </c>
       <c r="I46" t="n">
-        <v>8.413558483123779</v>
+        <v>7.684447288513184</v>
       </c>
       <c r="J46" t="n">
-        <v>7.520348787307739</v>
+        <v>7.283959150314331</v>
       </c>
       <c r="K46" t="n">
-        <v>7.323836326599121</v>
+        <v>7.023126840591431</v>
       </c>
       <c r="L46" t="n">
-        <v>7.883016967773438</v>
+        <v>7.749848961830139</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.091368436813354</v>
+        <v>8.111852645874023</v>
       </c>
       <c r="C47" t="n">
-        <v>9.245987892150879</v>
+        <v>7.862483739852905</v>
       </c>
       <c r="D47" t="n">
-        <v>8.3901047706604</v>
+        <v>8.328310012817383</v>
       </c>
       <c r="E47" t="n">
-        <v>8.194149732589722</v>
+        <v>8.325320959091187</v>
       </c>
       <c r="F47" t="n">
-        <v>8.487891674041748</v>
+        <v>7.887934446334839</v>
       </c>
       <c r="G47" t="n">
-        <v>8.318303108215332</v>
+        <v>8.015651702880859</v>
       </c>
       <c r="H47" t="n">
-        <v>7.973206281661987</v>
+        <v>9.073489665985107</v>
       </c>
       <c r="I47" t="n">
-        <v>9.414991855621338</v>
+        <v>9.009054660797119</v>
       </c>
       <c r="J47" t="n">
-        <v>8.006428003311157</v>
+        <v>8.676968097686768</v>
       </c>
       <c r="K47" t="n">
-        <v>8.771681308746338</v>
+        <v>8.525326013565063</v>
       </c>
       <c r="L47" t="n">
-        <v>8.489411306381225</v>
+        <v>8.381639194488525</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>6.318054437637329</v>
+        <v>7.102452754974365</v>
       </c>
       <c r="C48" t="n">
-        <v>7.189505100250244</v>
+        <v>6.741378784179688</v>
       </c>
       <c r="D48" t="n">
-        <v>8.169261455535889</v>
+        <v>6.461556911468506</v>
       </c>
       <c r="E48" t="n">
-        <v>7.957255840301514</v>
+        <v>6.453165054321289</v>
       </c>
       <c r="F48" t="n">
-        <v>7.240569114685059</v>
+        <v>6.690943002700806</v>
       </c>
       <c r="G48" t="n">
-        <v>6.640584230422974</v>
+        <v>6.692484378814697</v>
       </c>
       <c r="H48" t="n">
-        <v>6.777211904525757</v>
+        <v>6.858095645904541</v>
       </c>
       <c r="I48" t="n">
-        <v>6.93956995010376</v>
+        <v>7.041041374206543</v>
       </c>
       <c r="J48" t="n">
-        <v>6.758885622024536</v>
+        <v>6.775475263595581</v>
       </c>
       <c r="K48" t="n">
-        <v>7.056645393371582</v>
+        <v>6.496443748474121</v>
       </c>
       <c r="L48" t="n">
-        <v>7.104754304885864</v>
+        <v>6.731303691864014</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>7.649638414382935</v>
+        <v>7.025612592697144</v>
       </c>
       <c r="C49" t="n">
-        <v>7.114960193634033</v>
+        <v>7.204197645187378</v>
       </c>
       <c r="D49" t="n">
-        <v>7.335381746292114</v>
+        <v>7.337341547012329</v>
       </c>
       <c r="E49" t="n">
-        <v>7.073586940765381</v>
+        <v>7.231586933135986</v>
       </c>
       <c r="F49" t="n">
-        <v>7.053131341934204</v>
+        <v>7.136416673660278</v>
       </c>
       <c r="G49" t="n">
-        <v>8.641515970230103</v>
+        <v>8.142798662185669</v>
       </c>
       <c r="H49" t="n">
-        <v>7.614544868469238</v>
+        <v>7.377246856689453</v>
       </c>
       <c r="I49" t="n">
-        <v>7.651487112045288</v>
+        <v>7.668493747711182</v>
       </c>
       <c r="J49" t="n">
-        <v>7.265000581741333</v>
+        <v>7.297933340072632</v>
       </c>
       <c r="K49" t="n">
-        <v>7.295915842056274</v>
+        <v>6.945829153060913</v>
       </c>
       <c r="L49" t="n">
-        <v>7.469516301155091</v>
+        <v>7.336745715141296</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>7.870922088623047</v>
+        <v>9.151856422424316</v>
       </c>
       <c r="C50" t="n">
-        <v>8.306373596191406</v>
+        <v>7.769231796264648</v>
       </c>
       <c r="D50" t="n">
-        <v>7.819079160690308</v>
+        <v>7.844037532806396</v>
       </c>
       <c r="E50" t="n">
-        <v>8.092858076095581</v>
+        <v>8.183159351348877</v>
       </c>
       <c r="F50" t="n">
-        <v>7.697872638702393</v>
+        <v>8.720344305038452</v>
       </c>
       <c r="G50" t="n">
-        <v>7.596708297729492</v>
+        <v>7.529334545135498</v>
       </c>
       <c r="H50" t="n">
-        <v>7.978187799453735</v>
+        <v>8.787625551223755</v>
       </c>
       <c r="I50" t="n">
-        <v>7.97461462020874</v>
+        <v>7.239583492279053</v>
       </c>
       <c r="J50" t="n">
-        <v>8.322851896286011</v>
+        <v>7.644588708877563</v>
       </c>
       <c r="K50" t="n">
-        <v>7.504987001419067</v>
+        <v>7.527371168136597</v>
       </c>
       <c r="L50" t="n">
-        <v>7.916445517539978</v>
+        <v>8.039713287353516</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>7.116997718811035</v>
+        <v>8.323325872421265</v>
       </c>
       <c r="C51" t="n">
-        <v>8.131332635879517</v>
+        <v>7.176817893981934</v>
       </c>
       <c r="D51" t="n">
-        <v>7.601199865341187</v>
+        <v>7.751771211624146</v>
       </c>
       <c r="E51" t="n">
-        <v>6.915657043457031</v>
+        <v>6.806674718856812</v>
       </c>
       <c r="F51" t="n">
-        <v>7.920350551605225</v>
+        <v>7.642108678817749</v>
       </c>
       <c r="G51" t="n">
-        <v>7.912337303161621</v>
+        <v>7.555320024490356</v>
       </c>
       <c r="H51" t="n">
-        <v>7.308868646621704</v>
+        <v>7.00119161605835</v>
       </c>
       <c r="I51" t="n">
-        <v>7.167224884033203</v>
+        <v>7.171234369277954</v>
       </c>
       <c r="J51" t="n">
-        <v>7.912356853485107</v>
+        <v>7.65204644203186</v>
       </c>
       <c r="K51" t="n">
-        <v>8.150716066360474</v>
+        <v>7.870039939880371</v>
       </c>
       <c r="L51" t="n">
-        <v>7.613704156875611</v>
+        <v>7.49505307674408</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8.038214030265808</v>
+        <v>7.981467752456665</v>
       </c>
       <c r="C52" t="n">
-        <v>8.120459799766541</v>
+        <v>7.843910813331604</v>
       </c>
       <c r="D52" t="n">
-        <v>7.944863300323487</v>
+        <v>7.823853960037232</v>
       </c>
       <c r="E52" t="n">
-        <v>7.993344006538391</v>
+        <v>7.768391909599305</v>
       </c>
       <c r="F52" t="n">
-        <v>7.928898129463196</v>
+        <v>7.927794494628906</v>
       </c>
       <c r="G52" t="n">
-        <v>7.940275053977967</v>
+        <v>8.021658172607422</v>
       </c>
       <c r="H52" t="n">
-        <v>7.940179190635681</v>
+        <v>7.791833519935608</v>
       </c>
       <c r="I52" t="n">
-        <v>7.821307225227356</v>
+        <v>7.83490818977356</v>
       </c>
       <c r="J52" t="n">
-        <v>7.962496495246887</v>
+        <v>7.853196640014648</v>
       </c>
       <c r="K52" t="n">
-        <v>7.876464824676514</v>
+        <v>7.757974109649658</v>
       </c>
       <c r="L52" t="n">
-        <v>7.956650205612181</v>
+        <v>7.86049895620346</v>
       </c>
     </row>
   </sheetData>
